--- a/รายชื่อโรงพยาบาลและที่ตั้ง_แยกจังหวัด.xlsx
+++ b/รายชื่อโรงพยาบาลและที่ตั้ง_แยกจังหวัด.xlsx
@@ -5,22 +5,26 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Desktop\Download\ทำเว็บแอพ เช็ค รพ.ประกันสังคม 2569\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Desktop\Download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{957816F1-133E-4428-AA7B-3E34CD115EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC7D23F-F5C0-4C47-B8D3-084EC23B7A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="รายชื่อโรงพยาบาล " sheetId="4" r:id="rId1"/>
+    <sheet name="รพ. กรุงเทพมหานคร" sheetId="1" r:id="rId1"/>
+    <sheet name="รพ. ต่างจังหวัดและปริมณฑล" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="685">
+  <si>
+    <t>รายชื่อโรงพยาบาลและข้อมูลที่ตั้ง - รพ. กรุงเทพมหานคร</t>
+  </si>
   <si>
     <t>ลำดับ</t>
   </si>
@@ -385,6 +389,9 @@
     <t>รพ.ไอเอ็มเอช ธนบุรี</t>
   </si>
   <si>
+    <t>รายชื่อโรงพยาบาลและข้อมูลที่ตั้ง - รพ. ต่างจังหวัดและปริมณฑล</t>
+  </si>
+  <si>
     <t>รพ.กระบี่ (สธ)</t>
   </si>
   <si>
@@ -2069,9 +2076,6 @@
   </si>
   <si>
     <t>รพ.เฉลิมพระเกียรติสมเด็จพระเทพรัตนราชสุดาฯ สยามบรมราชกุมารี ระยอง (สธ)</t>
-  </si>
-  <si>
-    <t>รายชื่อโรงพยาบาลและข้อมูลที่ตั้ง</t>
   </si>
 </sst>
 </file>
@@ -2106,7 +2110,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2123,6 +2127,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F5F9"/>
         <bgColor rgb="FFF2F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E75B6"/>
+        <bgColor rgb="FF2E75B6"/>
       </patternFill>
     </fill>
   </fills>
@@ -2153,7 +2163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2169,6 +2179,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2475,41 +2488,41 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72897D64-4D7C-46A3-A58A-80204D9926C9}">
-  <dimension ref="A1:E275"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="70.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="77" customWidth="1"/>
+    <col min="3" max="3" width="39.5703125" customWidth="1"/>
+    <col min="4" max="4" width="37.42578125" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>683</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
     </row>
     <row r="3" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2517,16 +2530,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2534,16 +2547,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2551,16 +2564,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2568,16 +2581,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2585,16 +2598,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2602,16 +2615,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2619,16 +2632,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2636,16 +2649,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2653,16 +2666,16 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2670,16 +2683,16 @@
         <v>10</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2687,16 +2700,16 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2704,16 +2717,16 @@
         <v>12</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2721,16 +2734,16 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2738,16 +2751,16 @@
         <v>14</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2755,16 +2768,16 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2772,16 +2785,16 @@
         <v>16</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2789,16 +2802,16 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2806,16 +2819,16 @@
         <v>18</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2823,16 +2836,16 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2840,16 +2853,16 @@
         <v>20</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2857,16 +2870,16 @@
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2874,16 +2887,16 @@
         <v>22</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2891,16 +2904,16 @@
         <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2908,16 +2921,16 @@
         <v>24</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2925,16 +2938,16 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2942,16 +2955,16 @@
         <v>26</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2959,16 +2972,16 @@
         <v>27</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2976,16 +2989,16 @@
         <v>28</v>
       </c>
       <c r="B31" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>72</v>
-      </c>
       <c r="D31" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2993,16 +3006,16 @@
         <v>29</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3010,16 +3023,16 @@
         <v>30</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3027,16 +3040,16 @@
         <v>31</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3044,16 +3057,16 @@
         <v>32</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3061,16 +3074,16 @@
         <v>33</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3078,16 +3091,16 @@
         <v>34</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3095,16 +3108,16 @@
         <v>35</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3112,16 +3125,16 @@
         <v>36</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3129,16 +3142,16 @@
         <v>37</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3146,16 +3159,16 @@
         <v>38</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3163,16 +3176,16 @@
         <v>39</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3180,16 +3193,16 @@
         <v>40</v>
       </c>
       <c r="B43" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>98</v>
-      </c>
       <c r="E43" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3197,16 +3210,16 @@
         <v>41</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3214,16 +3227,16 @@
         <v>42</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3231,16 +3244,16 @@
         <v>43</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3248,16 +3261,16 @@
         <v>44</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3265,16 +3278,16 @@
         <v>45</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3282,16 +3295,16 @@
         <v>46</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3299,16 +3312,16 @@
         <v>47</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3316,16 +3329,16 @@
         <v>48</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3333,16 +3346,16 @@
         <v>49</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3350,33 +3363,929 @@
         <v>50</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E53" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E225"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="92.42578125" customWidth="1"/>
+    <col min="3" max="3" width="33" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="5" max="5" width="33" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="3" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>2</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>4</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>6</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
         <v>8</v>
       </c>
+      <c r="B11" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>10</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>12</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>14</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>16</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>18</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>19</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <v>20</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>22</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>682</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>24</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>25</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <v>26</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <v>28</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>29</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <v>30</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <v>32</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>33</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
+        <v>34</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>35</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
+        <v>36</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="4">
+        <v>38</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>39</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
+        <v>40</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>41</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="4">
+        <v>42</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>43</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="4">
+        <v>44</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>45</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="4">
+        <v>46</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>47</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="4">
+        <v>48</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>49</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="4">
+        <v>50</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>683</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="54" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="4">
+      <c r="A54" s="2">
         <v>51</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>121</v>
+        <v>247</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>122</v>
+        <v>248</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>123</v>
+        <v>249</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>124</v>
+        <v>250</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3384,33 +4293,33 @@
         <v>52</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>125</v>
+        <v>251</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>126</v>
+        <v>252</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>127</v>
+        <v>253</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>128</v>
+        <v>250</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="4">
+      <c r="A56" s="2">
         <v>53</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>129</v>
+        <v>254</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>130</v>
+        <v>255</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>127</v>
+        <v>256</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>128</v>
+        <v>250</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3418,33 +4327,33 @@
         <v>54</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>131</v>
+        <v>257</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>132</v>
+        <v>258</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>128</v>
+        <v>259</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="4">
+      <c r="A58" s="2">
         <v>55</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>133</v>
+        <v>260</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>135</v>
+        <v>262</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>136</v>
+        <v>263</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3452,33 +4361,33 @@
         <v>56</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>137</v>
+        <v>264</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>134</v>
+        <v>265</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>138</v>
+        <v>262</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>139</v>
+        <v>263</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="4">
+      <c r="A60" s="2">
         <v>57</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>140</v>
+        <v>266</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>134</v>
+        <v>267</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>141</v>
+        <v>267</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>142</v>
+        <v>263</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3486,33 +4395,33 @@
         <v>58</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>143</v>
+        <v>268</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>144</v>
+        <v>262</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>142</v>
+        <v>263</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="4">
+      <c r="A62" s="2">
         <v>59</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>134</v>
+        <v>270</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>142</v>
+        <v>263</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3520,33 +4429,33 @@
         <v>60</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>146</v>
+        <v>271</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>147</v>
+        <v>267</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>148</v>
+        <v>267</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>149</v>
+        <v>263</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="4">
+      <c r="A64" s="2">
         <v>61</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>150</v>
+        <v>272</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>152</v>
+        <v>262</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>153</v>
+        <v>263</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3554,33 +4463,33 @@
         <v>62</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>154</v>
+        <v>273</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>155</v>
+        <v>274</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>152</v>
+        <v>275</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>153</v>
+        <v>276</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="4">
+      <c r="A66" s="2">
         <v>63</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>156</v>
+        <v>277</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>157</v>
+        <v>278</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>158</v>
+        <v>279</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>153</v>
+        <v>276</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3588,33 +4497,33 @@
         <v>64</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>159</v>
+        <v>280</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>160</v>
+        <v>281</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>161</v>
+        <v>281</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>162</v>
+        <v>276</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="4">
+      <c r="A68" s="2">
         <v>65</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>163</v>
+        <v>282</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>165</v>
+        <v>275</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>162</v>
+        <v>276</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3622,33 +4531,33 @@
         <v>66</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>166</v>
+        <v>283</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>167</v>
+        <v>284</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>167</v>
+        <v>284</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>162</v>
+        <v>276</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="4">
+      <c r="A70" s="2">
         <v>67</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>168</v>
+        <v>285</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>169</v>
+        <v>286</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>170</v>
+        <v>281</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>162</v>
+        <v>276</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3656,33 +4565,33 @@
         <v>68</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>171</v>
+        <v>287</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>172</v>
+        <v>288</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>172</v>
+        <v>289</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>162</v>
+        <v>290</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="4">
+      <c r="A72" s="2">
         <v>69</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>173</v>
+        <v>291</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>164</v>
+        <v>292</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>165</v>
+        <v>289</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>162</v>
+        <v>290</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3690,33 +4599,33 @@
         <v>70</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>174</v>
+        <v>293</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>175</v>
+        <v>294</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>161</v>
+        <v>295</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>162</v>
+        <v>296</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="4">
+      <c r="A74" s="2">
         <v>71</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>176</v>
+        <v>297</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>177</v>
+        <v>298</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>172</v>
+        <v>299</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>162</v>
+        <v>296</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3724,33 +4633,33 @@
         <v>72</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>680</v>
+        <v>300</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>178</v>
+        <v>301</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>172</v>
+        <v>299</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>162</v>
+        <v>296</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="4">
+      <c r="A76" s="2">
         <v>73</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>179</v>
+        <v>302</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>172</v>
+        <v>294</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>172</v>
+        <v>295</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>162</v>
+        <v>296</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3758,33 +4667,33 @@
         <v>74</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>180</v>
+        <v>303</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>178</v>
+        <v>304</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>172</v>
+        <v>305</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>162</v>
+        <v>296</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="4">
+      <c r="A78" s="2">
         <v>75</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>181</v>
+        <v>306</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>182</v>
+        <v>295</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>161</v>
+        <v>295</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>162</v>
+        <v>296</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3792,33 +4701,33 @@
         <v>76</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>183</v>
+        <v>307</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>184</v>
+        <v>308</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>161</v>
+        <v>305</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>162</v>
+        <v>296</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="4">
+      <c r="A80" s="2">
         <v>77</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>185</v>
+        <v>309</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>186</v>
+        <v>310</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>172</v>
+        <v>311</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>162</v>
+        <v>312</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3826,33 +4735,33 @@
         <v>78</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>187</v>
+        <v>313</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>177</v>
+        <v>314</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>172</v>
+        <v>314</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>162</v>
+        <v>312</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="4">
+      <c r="A82" s="2">
         <v>79</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>188</v>
+        <v>315</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>189</v>
+        <v>310</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>190</v>
+        <v>311</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>191</v>
+        <v>312</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3860,33 +4769,33 @@
         <v>80</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>192</v>
+        <v>316</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>193</v>
+        <v>317</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>194</v>
+        <v>318</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="4">
+      <c r="A84" s="2">
         <v>81</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>195</v>
+        <v>319</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>196</v>
+        <v>320</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>197</v>
+        <v>320</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>198</v>
+        <v>321</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3894,33 +4803,33 @@
         <v>82</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>199</v>
+        <v>322</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>200</v>
+        <v>136</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>201</v>
+        <v>323</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>202</v>
+        <v>321</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="4">
+      <c r="A86" s="2">
         <v>83</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>203</v>
+        <v>324</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>204</v>
+        <v>325</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>201</v>
+        <v>326</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>202</v>
+        <v>325</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3928,33 +4837,33 @@
         <v>84</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>205</v>
+        <v>327</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>200</v>
+        <v>328</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>201</v>
+        <v>329</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>202</v>
+        <v>330</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="4">
+      <c r="A88" s="2">
         <v>85</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>206</v>
+        <v>331</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>207</v>
+        <v>332</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>208</v>
+        <v>333</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>209</v>
+        <v>330</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3962,33 +4871,33 @@
         <v>86</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>210</v>
+        <v>334</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>211</v>
+        <v>335</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>212</v>
+        <v>336</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>209</v>
+        <v>330</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="4">
+      <c r="A90" s="2">
         <v>87</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>213</v>
+        <v>337</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>214</v>
+        <v>328</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>215</v>
+        <v>329</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>209</v>
+        <v>330</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3996,33 +4905,33 @@
         <v>88</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>216</v>
+        <v>338</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>217</v>
+        <v>335</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>212</v>
+        <v>336</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>209</v>
+        <v>330</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="4">
+      <c r="A92" s="2">
         <v>89</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>218</v>
+        <v>339</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>219</v>
+        <v>340</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>212</v>
+        <v>341</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>209</v>
+        <v>330</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4030,33 +4939,33 @@
         <v>90</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>220</v>
+        <v>342</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>221</v>
+        <v>328</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>212</v>
+        <v>329</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>209</v>
+        <v>330</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="4">
+      <c r="A94" s="2">
         <v>91</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>222</v>
+        <v>343</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>223</v>
+        <v>340</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>212</v>
+        <v>341</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>209</v>
+        <v>330</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4064,33 +4973,33 @@
         <v>92</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>224</v>
+        <v>344</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>223</v>
+        <v>332</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>212</v>
+        <v>333</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>209</v>
+        <v>330</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="4">
+      <c r="A96" s="2">
         <v>93</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>225</v>
+        <v>345</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>226</v>
+        <v>335</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>227</v>
+        <v>336</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>228</v>
+        <v>330</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4098,33 +5007,33 @@
         <v>94</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>229</v>
+        <v>346</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>226</v>
+        <v>347</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>227</v>
+        <v>348</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>228</v>
+        <v>349</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="4">
+      <c r="A98" s="2">
         <v>95</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>230</v>
+        <v>350</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>155</v>
+        <v>351</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>231</v>
+        <v>352</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>232</v>
+        <v>349</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4132,33 +5041,33 @@
         <v>96</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>233</v>
+        <v>353</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>234</v>
+        <v>349</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>234</v>
+        <v>354</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>235</v>
+        <v>349</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="4">
+      <c r="A100" s="2">
         <v>97</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>236</v>
+        <v>355</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>237</v>
+        <v>356</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>238</v>
+        <v>356</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>235</v>
+        <v>349</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4166,33 +5075,33 @@
         <v>98</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>239</v>
+        <v>357</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>234</v>
+        <v>358</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>234</v>
+        <v>359</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>235</v>
+        <v>360</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="4">
+      <c r="A102" s="2">
         <v>99</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>240</v>
+        <v>361</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>241</v>
+        <v>153</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>242</v>
+        <v>362</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>241</v>
+        <v>360</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4200,33 +5109,33 @@
         <v>100</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>681</v>
+        <v>363</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>243</v>
+        <v>364</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>244</v>
+        <v>362</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>241</v>
+        <v>360</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="4">
+      <c r="A104" s="2">
         <v>101</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>245</v>
+        <v>365</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>246</v>
+        <v>366</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>247</v>
+        <v>367</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>248</v>
+        <v>360</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4234,33 +5143,33 @@
         <v>102</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>249</v>
+        <v>368</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>250</v>
+        <v>366</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>251</v>
+        <v>367</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>248</v>
+        <v>360</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="4">
+      <c r="A106" s="2">
         <v>103</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>252</v>
+        <v>369</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>253</v>
+        <v>370</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>254</v>
+        <v>371</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>248</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4268,33 +5177,33 @@
         <v>104</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>255</v>
+        <v>373</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>134</v>
+        <v>374</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>256</v>
+        <v>375</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>257</v>
+        <v>375</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="4">
+      <c r="A108" s="2">
         <v>105</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>258</v>
+        <v>376</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>259</v>
+        <v>377</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>260</v>
+        <v>377</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>261</v>
+        <v>375</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4302,33 +5211,33 @@
         <v>106</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>262</v>
+        <v>378</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>263</v>
+        <v>379</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>260</v>
+        <v>380</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>261</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="4">
+      <c r="A110" s="2">
         <v>107</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>264</v>
+        <v>381</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>265</v>
+        <v>382</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>265</v>
+        <v>375</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>261</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4336,33 +5245,33 @@
         <v>108</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>266</v>
+        <v>383</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>134</v>
+        <v>379</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>260</v>
+        <v>380</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>261</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="4">
+      <c r="A112" s="2">
         <v>109</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>267</v>
+        <v>384</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>268</v>
+        <v>385</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>260</v>
+        <v>386</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>261</v>
+        <v>387</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4370,33 +5279,33 @@
         <v>110</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>269</v>
+        <v>388</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>265</v>
+        <v>389</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>265</v>
+        <v>390</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>261</v>
+        <v>387</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="4">
+      <c r="A114" s="2">
         <v>111</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>270</v>
+        <v>391</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>134</v>
+        <v>392</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>260</v>
+        <v>390</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>261</v>
+        <v>387</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4404,33 +5313,33 @@
         <v>112</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>271</v>
+        <v>393</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>272</v>
+        <v>394</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>273</v>
+        <v>395</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>274</v>
+        <v>396</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="4">
+      <c r="A116" s="2">
         <v>113</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>275</v>
+        <v>397</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>276</v>
+        <v>398</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>277</v>
+        <v>399</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>274</v>
+        <v>396</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4438,33 +5347,33 @@
         <v>114</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>278</v>
+        <v>400</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>279</v>
+        <v>401</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>279</v>
+        <v>402</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>274</v>
+        <v>403</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="4">
+      <c r="A118" s="2">
         <v>115</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>280</v>
+        <v>404</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>273</v>
+        <v>405</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>274</v>
+        <v>406</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4472,33 +5381,33 @@
         <v>116</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>281</v>
+        <v>407</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>282</v>
+        <v>408</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>282</v>
+        <v>409</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>274</v>
+        <v>410</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="4">
+      <c r="A120" s="2">
         <v>117</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>283</v>
+        <v>411</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>284</v>
+        <v>136</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>279</v>
+        <v>409</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>274</v>
+        <v>410</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4506,33 +5415,33 @@
         <v>118</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>285</v>
+        <v>412</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>286</v>
+        <v>413</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>287</v>
+        <v>409</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>288</v>
+        <v>410</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="4">
+      <c r="A122" s="2">
         <v>119</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>289</v>
+        <v>414</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>290</v>
+        <v>136</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>287</v>
+        <v>409</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>288</v>
+        <v>410</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4540,33 +5449,33 @@
         <v>120</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>291</v>
+        <v>415</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>292</v>
+        <v>416</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>293</v>
+        <v>417</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>294</v>
+        <v>418</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="4">
+      <c r="A124" s="2">
         <v>121</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>295</v>
+        <v>419</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>296</v>
+        <v>136</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>297</v>
+        <v>420</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>294</v>
+        <v>421</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4574,33 +5483,33 @@
         <v>122</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>298</v>
+        <v>422</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>299</v>
+        <v>136</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>297</v>
+        <v>423</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>294</v>
+        <v>424</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="4">
+      <c r="A126" s="2">
         <v>123</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>300</v>
+        <v>425</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>292</v>
+        <v>426</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>293</v>
+        <v>427</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>294</v>
+        <v>428</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4608,33 +5517,33 @@
         <v>124</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>301</v>
+        <v>429</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>302</v>
+        <v>430</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>303</v>
+        <v>431</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>294</v>
+        <v>428</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="4">
+      <c r="A128" s="2">
         <v>125</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>304</v>
+        <v>432</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>293</v>
+        <v>430</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>293</v>
+        <v>431</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>294</v>
+        <v>428</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4642,33 +5551,33 @@
         <v>126</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>305</v>
+        <v>433</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>306</v>
+        <v>434</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>303</v>
+        <v>431</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>294</v>
+        <v>428</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="4">
+      <c r="A130" s="2">
         <v>127</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>307</v>
+        <v>435</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>308</v>
+        <v>436</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>309</v>
+        <v>431</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>310</v>
+        <v>428</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4676,33 +5585,33 @@
         <v>128</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>311</v>
+        <v>437</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>312</v>
+        <v>438</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>312</v>
+        <v>439</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>310</v>
+        <v>440</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="4">
+      <c r="A132" s="2">
         <v>129</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>313</v>
+        <v>441</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>308</v>
+        <v>438</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>309</v>
+        <v>439</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>310</v>
+        <v>440</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4710,33 +5619,33 @@
         <v>130</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>314</v>
+        <v>442</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>134</v>
+        <v>443</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>315</v>
+        <v>444</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>316</v>
+        <v>443</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="4">
+      <c r="A134" s="2">
         <v>131</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>317</v>
+        <v>445</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>318</v>
+        <v>446</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>318</v>
+        <v>447</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>319</v>
+        <v>448</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4744,33 +5653,33 @@
         <v>132</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>320</v>
+        <v>449</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>134</v>
+        <v>450</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>321</v>
+        <v>451</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>319</v>
+        <v>452</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="4">
+      <c r="A136" s="2">
         <v>133</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>322</v>
+        <v>453</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>323</v>
+        <v>454</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>324</v>
+        <v>454</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>323</v>
+        <v>455</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4778,33 +5687,33 @@
         <v>134</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>325</v>
+        <v>456</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>326</v>
+        <v>457</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>327</v>
+        <v>458</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>328</v>
+        <v>455</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="4">
+      <c r="A138" s="2">
         <v>135</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>329</v>
+        <v>459</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>330</v>
+        <v>136</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>331</v>
+        <v>460</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>328</v>
+        <v>461</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4812,33 +5721,33 @@
         <v>136</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>332</v>
+        <v>462</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>333</v>
+        <v>463</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>334</v>
+        <v>464</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>328</v>
+        <v>465</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="4">
+      <c r="A140" s="2">
         <v>137</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>335</v>
+        <v>466</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>326</v>
+        <v>467</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>327</v>
+        <v>468</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>328</v>
+        <v>469</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4846,33 +5755,33 @@
         <v>138</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>336</v>
+        <v>470</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>333</v>
+        <v>471</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>334</v>
+        <v>468</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>328</v>
+        <v>469</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="4">
+      <c r="A142" s="2">
         <v>139</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>337</v>
+        <v>472</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>338</v>
+        <v>473</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>339</v>
+        <v>468</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>328</v>
+        <v>469</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4880,33 +5789,33 @@
         <v>140</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>340</v>
+        <v>684</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>326</v>
+        <v>474</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>327</v>
+        <v>468</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>328</v>
+        <v>469</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="4">
+      <c r="A144" s="2">
         <v>141</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>341</v>
+        <v>475</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>338</v>
+        <v>476</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>339</v>
+        <v>476</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>328</v>
+        <v>469</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4914,33 +5823,33 @@
         <v>142</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>342</v>
+        <v>477</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>330</v>
+        <v>478</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>331</v>
+        <v>476</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>328</v>
+        <v>469</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="4">
+      <c r="A146" s="2">
         <v>143</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>343</v>
+        <v>479</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>333</v>
+        <v>480</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>334</v>
+        <v>480</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>328</v>
+        <v>481</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4948,33 +5857,33 @@
         <v>144</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>344</v>
+        <v>482</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>345</v>
+        <v>483</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>346</v>
+        <v>483</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>347</v>
+        <v>481</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="4">
+      <c r="A148" s="2">
         <v>145</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>348</v>
+        <v>484</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>349</v>
+        <v>485</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>350</v>
+        <v>485</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>347</v>
+        <v>481</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4982,33 +5891,33 @@
         <v>146</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>351</v>
+        <v>486</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>347</v>
+        <v>153</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>352</v>
+        <v>487</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>347</v>
+        <v>481</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="4">
+      <c r="A150" s="2">
         <v>147</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>353</v>
+        <v>488</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>354</v>
+        <v>483</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>354</v>
+        <v>483</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>347</v>
+        <v>481</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5016,33 +5925,33 @@
         <v>148</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>355</v>
+        <v>489</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>356</v>
+        <v>490</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>357</v>
+        <v>490</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>358</v>
+        <v>491</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="4">
+      <c r="A152" s="2">
         <v>149</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>359</v>
+        <v>492</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>151</v>
+        <v>493</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>360</v>
+        <v>494</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>358</v>
+        <v>491</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5050,33 +5959,33 @@
         <v>150</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>361</v>
+        <v>495</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>362</v>
+        <v>496</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>360</v>
+        <v>494</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>358</v>
+        <v>491</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="4">
+      <c r="A154" s="2">
         <v>151</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>363</v>
+        <v>497</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>364</v>
+        <v>498</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>365</v>
+        <v>499</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>358</v>
+        <v>500</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5084,33 +5993,33 @@
         <v>152</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>366</v>
+        <v>501</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>364</v>
+        <v>502</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>365</v>
+        <v>499</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>358</v>
+        <v>500</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="4">
+      <c r="A156" s="2">
         <v>153</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>367</v>
+        <v>503</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>368</v>
+        <v>504</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>369</v>
+        <v>505</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>370</v>
+        <v>506</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5118,33 +6027,33 @@
         <v>154</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>371</v>
+        <v>507</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>372</v>
+        <v>508</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>373</v>
+        <v>505</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>373</v>
+        <v>506</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="4">
+      <c r="A158" s="2">
         <v>155</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>374</v>
+        <v>509</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>375</v>
+        <v>136</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>375</v>
+        <v>505</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>373</v>
+        <v>506</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5152,33 +6061,33 @@
         <v>156</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>376</v>
+        <v>510</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>377</v>
+        <v>511</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>378</v>
+        <v>505</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>373</v>
+        <v>506</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="4">
+      <c r="A160" s="2">
         <v>157</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>379</v>
+        <v>512</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>380</v>
+        <v>513</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>373</v>
+        <v>514</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>373</v>
+        <v>515</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5186,33 +6095,33 @@
         <v>158</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>381</v>
+        <v>516</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>377</v>
+        <v>517</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>378</v>
+        <v>518</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>373</v>
+        <v>519</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="4">
+      <c r="A162" s="2">
         <v>159</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>382</v>
+        <v>520</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>383</v>
+        <v>521</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>384</v>
+        <v>522</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>385</v>
+        <v>523</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5220,33 +6129,33 @@
         <v>160</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>386</v>
+        <v>524</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>387</v>
+        <v>525</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>388</v>
+        <v>525</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>385</v>
+        <v>523</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="4">
+      <c r="A164" s="2">
         <v>161</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>389</v>
+        <v>526</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>390</v>
+        <v>527</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>388</v>
+        <v>528</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>385</v>
+        <v>529</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5254,33 +6163,33 @@
         <v>162</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>391</v>
+        <v>530</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>392</v>
+        <v>531</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>393</v>
+        <v>532</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>394</v>
+        <v>529</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="4">
+      <c r="A166" s="2">
         <v>163</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>395</v>
+        <v>533</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>396</v>
+        <v>532</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>397</v>
+        <v>532</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>394</v>
+        <v>529</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5288,33 +6197,33 @@
         <v>164</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>398</v>
+        <v>534</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>399</v>
+        <v>532</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>400</v>
+        <v>532</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>401</v>
+        <v>529</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="4">
+      <c r="A168" s="2">
         <v>165</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>402</v>
+        <v>535</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>134</v>
+        <v>536</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>403</v>
+        <v>537</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>404</v>
+        <v>538</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5322,33 +6231,33 @@
         <v>166</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>405</v>
+        <v>539</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>406</v>
+        <v>540</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>407</v>
+        <v>540</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>408</v>
+        <v>541</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="4">
+      <c r="A170" s="2">
         <v>167</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>409</v>
+        <v>542</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>134</v>
+        <v>543</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>407</v>
+        <v>544</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>408</v>
+        <v>541</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5356,33 +6265,33 @@
         <v>168</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>410</v>
+        <v>545</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>411</v>
+        <v>124</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>407</v>
+        <v>546</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>408</v>
+        <v>541</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="4">
+      <c r="A172" s="2">
         <v>169</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>412</v>
+        <v>547</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>134</v>
+        <v>548</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>407</v>
+        <v>544</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>408</v>
+        <v>541</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5390,33 +6299,33 @@
         <v>170</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>413</v>
+        <v>549</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>414</v>
+        <v>548</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>415</v>
+        <v>544</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>416</v>
+        <v>541</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="4">
+      <c r="A174" s="2">
         <v>171</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>417</v>
+        <v>550</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>134</v>
+        <v>551</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>418</v>
+        <v>544</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>419</v>
+        <v>541</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5424,33 +6333,33 @@
         <v>172</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>420</v>
+        <v>552</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>134</v>
+        <v>543</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>421</v>
+        <v>544</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>422</v>
+        <v>541</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="4">
+      <c r="A176" s="2">
         <v>173</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>423</v>
+        <v>553</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>424</v>
+        <v>554</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>425</v>
+        <v>554</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>426</v>
+        <v>541</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5458,33 +6367,33 @@
         <v>174</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>427</v>
+        <v>555</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>428</v>
+        <v>543</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>429</v>
+        <v>544</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>426</v>
+        <v>541</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="4">
+      <c r="A178" s="2">
         <v>175</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>430</v>
+        <v>556</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>428</v>
+        <v>124</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>429</v>
+        <v>546</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>426</v>
+        <v>541</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5492,33 +6401,33 @@
         <v>176</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>431</v>
+        <v>557</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>432</v>
+        <v>540</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>429</v>
+        <v>540</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>426</v>
+        <v>541</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="4">
+      <c r="A180" s="2">
         <v>177</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>433</v>
+        <v>558</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>434</v>
+        <v>559</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>429</v>
+        <v>546</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>426</v>
+        <v>541</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5526,33 +6435,33 @@
         <v>178</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>435</v>
+        <v>560</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>436</v>
+        <v>561</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>437</v>
+        <v>546</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>438</v>
+        <v>541</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="4">
+      <c r="A182" s="2">
         <v>179</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>439</v>
+        <v>562</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>436</v>
+        <v>563</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>437</v>
+        <v>564</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>438</v>
+        <v>541</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5560,33 +6469,33 @@
         <v>180</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>440</v>
+        <v>565</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>441</v>
+        <v>566</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>442</v>
+        <v>564</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>441</v>
+        <v>541</v>
       </c>
     </row>
     <row r="184" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="4">
+      <c r="A184" s="2">
         <v>181</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>443</v>
+        <v>567</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>444</v>
+        <v>124</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>445</v>
+        <v>546</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>446</v>
+        <v>541</v>
       </c>
     </row>
     <row r="185" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5594,33 +6503,33 @@
         <v>182</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>447</v>
+        <v>568</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>448</v>
+        <v>569</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>449</v>
+        <v>564</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>450</v>
+        <v>541</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="4">
+      <c r="A186" s="2">
         <v>183</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>451</v>
+        <v>570</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>452</v>
+        <v>571</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>452</v>
+        <v>572</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>453</v>
+        <v>573</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5628,33 +6537,33 @@
         <v>184</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>454</v>
+        <v>574</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>455</v>
+        <v>575</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>456</v>
+        <v>576</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>453</v>
+        <v>577</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="4">
+      <c r="A188" s="2">
         <v>185</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>457</v>
+        <v>578</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>134</v>
+        <v>579</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>458</v>
+        <v>579</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>459</v>
+        <v>577</v>
       </c>
     </row>
     <row r="189" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5662,33 +6571,33 @@
         <v>186</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>460</v>
+        <v>580</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>461</v>
+        <v>581</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>462</v>
+        <v>582</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>463</v>
+        <v>577</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="4">
+      <c r="A190" s="2">
         <v>187</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>464</v>
+        <v>583</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>465</v>
+        <v>584</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>466</v>
+        <v>576</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>467</v>
+        <v>577</v>
       </c>
     </row>
     <row r="191" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5696,33 +6605,33 @@
         <v>188</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>468</v>
+        <v>585</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>469</v>
+        <v>586</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>466</v>
+        <v>582</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>467</v>
+        <v>577</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="4">
+      <c r="A192" s="2">
         <v>189</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>470</v>
+        <v>587</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>471</v>
+        <v>588</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>466</v>
+        <v>582</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>467</v>
+        <v>577</v>
       </c>
     </row>
     <row r="193" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5730,33 +6639,33 @@
         <v>190</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>682</v>
+        <v>589</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>472</v>
+        <v>584</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>466</v>
+        <v>576</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>467</v>
+        <v>577</v>
       </c>
     </row>
     <row r="194" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="4">
+      <c r="A194" s="2">
         <v>191</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>473</v>
+        <v>590</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>474</v>
+        <v>591</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>474</v>
+        <v>582</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>467</v>
+        <v>577</v>
       </c>
     </row>
     <row r="195" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5764,33 +6673,33 @@
         <v>192</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>475</v>
+        <v>592</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>476</v>
+        <v>593</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>474</v>
+        <v>594</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>467</v>
+        <v>593</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="4">
+      <c r="A196" s="2">
         <v>193</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>477</v>
+        <v>595</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>478</v>
+        <v>596</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>478</v>
+        <v>596</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>479</v>
+        <v>597</v>
       </c>
     </row>
     <row r="197" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5798,33 +6707,33 @@
         <v>194</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>480</v>
+        <v>598</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>481</v>
+        <v>599</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>481</v>
+        <v>600</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>479</v>
+        <v>597</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="4">
+      <c r="A198" s="2">
         <v>195</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>482</v>
+        <v>601</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>483</v>
+        <v>599</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>483</v>
+        <v>600</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>479</v>
+        <v>597</v>
       </c>
     </row>
     <row r="199" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5832,33 +6741,33 @@
         <v>196</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>484</v>
+        <v>602</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>151</v>
+        <v>603</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>485</v>
+        <v>604</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>479</v>
+        <v>605</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="4">
+      <c r="A200" s="2">
         <v>197</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>486</v>
+        <v>606</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>481</v>
+        <v>607</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>481</v>
+        <v>607</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>479</v>
+        <v>605</v>
       </c>
     </row>
     <row r="201" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5866,33 +6775,33 @@
         <v>198</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>487</v>
+        <v>608</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>488</v>
+        <v>609</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>488</v>
+        <v>610</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>489</v>
+        <v>611</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="4">
+      <c r="A202" s="2">
         <v>199</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>490</v>
+        <v>612</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>491</v>
+        <v>613</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>492</v>
+        <v>614</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>489</v>
+        <v>611</v>
       </c>
     </row>
     <row r="203" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5900,33 +6809,33 @@
         <v>200</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>493</v>
+        <v>615</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>494</v>
+        <v>616</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>492</v>
+        <v>617</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>489</v>
+        <v>618</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="4">
+      <c r="A204" s="2">
         <v>201</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>495</v>
+        <v>619</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>496</v>
+        <v>620</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>497</v>
+        <v>620</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>498</v>
+        <v>618</v>
       </c>
     </row>
     <row r="205" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5934,33 +6843,33 @@
         <v>202</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>499</v>
+        <v>621</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>500</v>
+        <v>622</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>497</v>
+        <v>622</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>498</v>
+        <v>618</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A206" s="4">
+      <c r="A206" s="2">
         <v>203</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>501</v>
+        <v>623</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>502</v>
+        <v>624</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>503</v>
+        <v>625</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>504</v>
+        <v>626</v>
       </c>
     </row>
     <row r="207" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5968,33 +6877,33 @@
         <v>204</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>505</v>
+        <v>627</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>506</v>
+        <v>438</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>503</v>
+        <v>628</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>504</v>
+        <v>626</v>
       </c>
     </row>
     <row r="208" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="4">
+      <c r="A208" s="2">
         <v>205</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>507</v>
+        <v>629</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>134</v>
+        <v>630</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>503</v>
+        <v>631</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>504</v>
+        <v>626</v>
       </c>
     </row>
     <row r="209" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6002,33 +6911,33 @@
         <v>206</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>508</v>
+        <v>632</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>509</v>
+        <v>633</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>503</v>
+        <v>625</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>504</v>
+        <v>626</v>
       </c>
     </row>
     <row r="210" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="4">
+      <c r="A210" s="2">
         <v>207</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>510</v>
+        <v>634</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>511</v>
+        <v>136</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>512</v>
+        <v>635</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>513</v>
+        <v>636</v>
       </c>
     </row>
     <row r="211" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6036,33 +6945,33 @@
         <v>208</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>514</v>
+        <v>637</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>515</v>
+        <v>638</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>516</v>
+        <v>638</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>517</v>
+        <v>639</v>
       </c>
     </row>
     <row r="212" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A212" s="4">
+      <c r="A212" s="2">
         <v>209</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>518</v>
+        <v>640</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>519</v>
+        <v>136</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>520</v>
+        <v>641</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>521</v>
+        <v>639</v>
       </c>
     </row>
     <row r="213" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6070,33 +6979,33 @@
         <v>210</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>522</v>
+        <v>642</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>523</v>
+        <v>643</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>523</v>
+        <v>644</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>521</v>
+        <v>645</v>
       </c>
     </row>
     <row r="214" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="4">
+      <c r="A214" s="2">
         <v>211</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>524</v>
+        <v>646</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>525</v>
+        <v>647</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>526</v>
+        <v>648</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>527</v>
+        <v>624</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6104,33 +7013,33 @@
         <v>212</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>528</v>
+        <v>649</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>529</v>
+        <v>650</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>530</v>
+        <v>651</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>527</v>
+        <v>652</v>
       </c>
     </row>
     <row r="216" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A216" s="4">
+      <c r="A216" s="2">
         <v>213</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>531</v>
+        <v>653</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>530</v>
+        <v>654</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>530</v>
+        <v>655</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>527</v>
+        <v>656</v>
       </c>
     </row>
     <row r="217" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6138,33 +7047,33 @@
         <v>214</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>532</v>
+        <v>657</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>530</v>
+        <v>658</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>530</v>
+        <v>659</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>527</v>
+        <v>656</v>
       </c>
     </row>
     <row r="218" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A218" s="4">
+      <c r="A218" s="2">
         <v>215</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>533</v>
+        <v>660</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>534</v>
+        <v>661</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>535</v>
+        <v>659</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>536</v>
+        <v>656</v>
       </c>
     </row>
     <row r="219" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6172,33 +7081,33 @@
         <v>216</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>537</v>
+        <v>662</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>538</v>
+        <v>663</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>538</v>
+        <v>663</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>539</v>
+        <v>656</v>
       </c>
     </row>
     <row r="220" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A220" s="4">
+      <c r="A220" s="2">
         <v>217</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>540</v>
+        <v>664</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>541</v>
+        <v>665</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>542</v>
+        <v>666</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>539</v>
+        <v>667</v>
       </c>
     </row>
     <row r="221" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6206,33 +7115,33 @@
         <v>218</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>543</v>
+        <v>668</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>122</v>
+        <v>669</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>544</v>
+        <v>670</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>539</v>
+        <v>671</v>
       </c>
     </row>
     <row r="222" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="4">
+      <c r="A222" s="2">
         <v>219</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>545</v>
+        <v>672</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>546</v>
+        <v>177</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>542</v>
+        <v>673</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>539</v>
+        <v>674</v>
       </c>
     </row>
     <row r="223" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6240,33 +7149,33 @@
         <v>220</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>547</v>
+        <v>675</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>546</v>
+        <v>676</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>542</v>
+        <v>673</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>539</v>
+        <v>674</v>
       </c>
     </row>
     <row r="224" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A224" s="4">
+      <c r="A224" s="2">
         <v>221</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>548</v>
+        <v>677</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>549</v>
+        <v>136</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>542</v>
+        <v>678</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>539</v>
+        <v>674</v>
       </c>
     </row>
     <row r="225" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6274,866 +7183,16 @@
         <v>222</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>550</v>
+        <v>679</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>541</v>
+        <v>680</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>542</v>
+        <v>681</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A226" s="4">
-        <v>223</v>
-      </c>
-      <c r="B226" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="C226" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="D226" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="E226" s="3" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A227" s="4">
-        <v>224</v>
-      </c>
-      <c r="B227" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="C227" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="D227" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="E227" s="5" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A228" s="4">
-        <v>225</v>
-      </c>
-      <c r="B228" s="3" t="s">
-        <v>554</v>
-      </c>
-      <c r="C228" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D228" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="E228" s="3" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A229" s="4">
-        <v>226</v>
-      </c>
-      <c r="B229" s="5" t="s">
-        <v>555</v>
-      </c>
-      <c r="C229" s="5" t="s">
-        <v>538</v>
-      </c>
-      <c r="D229" s="5" t="s">
-        <v>538</v>
-      </c>
-      <c r="E229" s="5" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A230" s="4">
-        <v>227</v>
-      </c>
-      <c r="B230" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="C230" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="D230" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="E230" s="3" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="231" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A231" s="4">
-        <v>228</v>
-      </c>
-      <c r="B231" s="5" t="s">
-        <v>558</v>
-      </c>
-      <c r="C231" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="D231" s="5" t="s">
-        <v>544</v>
-      </c>
-      <c r="E231" s="5" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A232" s="4">
-        <v>229</v>
-      </c>
-      <c r="B232" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="C232" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D232" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="E232" s="3" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="233" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A233" s="4">
-        <v>230</v>
-      </c>
-      <c r="B233" s="5" t="s">
-        <v>563</v>
-      </c>
-      <c r="C233" s="5" t="s">
-        <v>564</v>
-      </c>
-      <c r="D233" s="5" t="s">
-        <v>562</v>
-      </c>
-      <c r="E233" s="5" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A234" s="4">
-        <v>231</v>
-      </c>
-      <c r="B234" s="3" t="s">
-        <v>565</v>
-      </c>
-      <c r="C234" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D234" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="E234" s="3" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A235" s="4">
-        <v>232</v>
-      </c>
-      <c r="B235" s="5" t="s">
-        <v>566</v>
-      </c>
-      <c r="C235" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="D235" s="5" t="s">
-        <v>562</v>
-      </c>
-      <c r="E235" s="5" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="236" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="4">
-        <v>233</v>
-      </c>
-      <c r="B236" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="C236" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="E236" s="3" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="4">
-        <v>234</v>
-      </c>
-      <c r="B237" s="5" t="s">
-        <v>572</v>
-      </c>
-      <c r="C237" s="5" t="s">
-        <v>573</v>
-      </c>
-      <c r="D237" s="5" t="s">
-        <v>574</v>
-      </c>
-      <c r="E237" s="5" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A238" s="4">
-        <v>235</v>
-      </c>
-      <c r="B238" s="3" t="s">
-        <v>576</v>
-      </c>
-      <c r="C238" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="D238" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="E238" s="3" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A239" s="4">
-        <v>236</v>
-      </c>
-      <c r="B239" s="5" t="s">
-        <v>578</v>
-      </c>
-      <c r="C239" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="D239" s="5" t="s">
-        <v>580</v>
-      </c>
-      <c r="E239" s="5" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A240" s="4">
-        <v>237</v>
-      </c>
-      <c r="B240" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="C240" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="D240" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="E240" s="3" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="4">
-        <v>238</v>
-      </c>
-      <c r="B241" s="5" t="s">
-        <v>583</v>
-      </c>
-      <c r="C241" s="5" t="s">
-        <v>584</v>
-      </c>
-      <c r="D241" s="5" t="s">
-        <v>580</v>
-      </c>
-      <c r="E241" s="5" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="242" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="4">
-        <v>239</v>
-      </c>
-      <c r="B242" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="C242" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="D242" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="E242" s="3" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="243" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A243" s="4">
-        <v>240</v>
-      </c>
-      <c r="B243" s="5" t="s">
-        <v>587</v>
-      </c>
-      <c r="C243" s="5" t="s">
-        <v>582</v>
-      </c>
-      <c r="D243" s="5" t="s">
-        <v>574</v>
-      </c>
-      <c r="E243" s="5" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="244" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A244" s="4">
-        <v>241</v>
-      </c>
-      <c r="B244" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="C244" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="D244" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="E244" s="3" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="245" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A245" s="4">
-        <v>242</v>
-      </c>
-      <c r="B245" s="5" t="s">
-        <v>590</v>
-      </c>
-      <c r="C245" s="5" t="s">
-        <v>591</v>
-      </c>
-      <c r="D245" s="5" t="s">
-        <v>592</v>
-      </c>
-      <c r="E245" s="5" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A246" s="4">
-        <v>243</v>
-      </c>
-      <c r="B246" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="C246" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="D246" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="E246" s="3" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A247" s="4">
-        <v>244</v>
-      </c>
-      <c r="B247" s="5" t="s">
-        <v>596</v>
-      </c>
-      <c r="C247" s="5" t="s">
-        <v>597</v>
-      </c>
-      <c r="D247" s="5" t="s">
-        <v>598</v>
-      </c>
-      <c r="E247" s="5" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="248" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A248" s="4">
-        <v>245</v>
-      </c>
-      <c r="B248" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="C248" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="D248" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="E248" s="3" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="249" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A249" s="4">
-        <v>246</v>
-      </c>
-      <c r="B249" s="5" t="s">
-        <v>600</v>
-      </c>
-      <c r="C249" s="5" t="s">
-        <v>601</v>
-      </c>
-      <c r="D249" s="5" t="s">
-        <v>602</v>
-      </c>
-      <c r="E249" s="5" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="250" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A250" s="4">
-        <v>247</v>
-      </c>
-      <c r="B250" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C250" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="D250" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="E250" s="3" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="251" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A251" s="4">
-        <v>248</v>
-      </c>
-      <c r="B251" s="5" t="s">
-        <v>606</v>
-      </c>
-      <c r="C251" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="D251" s="5" t="s">
-        <v>608</v>
-      </c>
-      <c r="E251" s="5" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A252" s="4">
-        <v>249</v>
-      </c>
-      <c r="B252" s="3" t="s">
-        <v>610</v>
-      </c>
-      <c r="C252" s="3" t="s">
-        <v>611</v>
-      </c>
-      <c r="D252" s="3" t="s">
-        <v>612</v>
-      </c>
-      <c r="E252" s="3" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A253" s="4">
-        <v>250</v>
-      </c>
-      <c r="B253" s="5" t="s">
-        <v>613</v>
-      </c>
-      <c r="C253" s="5" t="s">
-        <v>614</v>
-      </c>
-      <c r="D253" s="5" t="s">
-        <v>615</v>
-      </c>
-      <c r="E253" s="5" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="4">
-        <v>251</v>
-      </c>
-      <c r="B254" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="C254" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="D254" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="E254" s="3" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="255" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A255" s="4">
-        <v>252</v>
-      </c>
-      <c r="B255" s="5" t="s">
-        <v>619</v>
-      </c>
-      <c r="C255" s="5" t="s">
-        <v>620</v>
-      </c>
-      <c r="D255" s="5" t="s">
-        <v>620</v>
-      </c>
-      <c r="E255" s="5" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="256" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A256" s="4">
-        <v>253</v>
-      </c>
-      <c r="B256" s="3" t="s">
-        <v>621</v>
-      </c>
-      <c r="C256" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="D256" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="E256" s="3" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="257" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A257" s="4">
-        <v>254</v>
-      </c>
-      <c r="B257" s="5" t="s">
-        <v>625</v>
-      </c>
-      <c r="C257" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="D257" s="5" t="s">
-        <v>626</v>
-      </c>
-      <c r="E257" s="5" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="258" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A258" s="4">
-        <v>255</v>
-      </c>
-      <c r="B258" s="3" t="s">
-        <v>627</v>
-      </c>
-      <c r="C258" s="3" t="s">
-        <v>628</v>
-      </c>
-      <c r="D258" s="3" t="s">
-        <v>629</v>
-      </c>
-      <c r="E258" s="3" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="259" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A259" s="4">
-        <v>256</v>
-      </c>
-      <c r="B259" s="5" t="s">
-        <v>630</v>
-      </c>
-      <c r="C259" s="5" t="s">
-        <v>631</v>
-      </c>
-      <c r="D259" s="5" t="s">
-        <v>623</v>
-      </c>
-      <c r="E259" s="5" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="260" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A260" s="4">
-        <v>257</v>
-      </c>
-      <c r="B260" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="C260" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D260" s="3" t="s">
-        <v>633</v>
-      </c>
-      <c r="E260" s="3" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="261" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A261" s="4">
-        <v>258</v>
-      </c>
-      <c r="B261" s="5" t="s">
-        <v>635</v>
-      </c>
-      <c r="C261" s="5" t="s">
-        <v>636</v>
-      </c>
-      <c r="D261" s="5" t="s">
-        <v>636</v>
-      </c>
-      <c r="E261" s="5" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="262" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A262" s="4">
-        <v>259</v>
-      </c>
-      <c r="B262" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="C262" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D262" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="E262" s="3" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="263" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A263" s="4">
-        <v>260</v>
-      </c>
-      <c r="B263" s="5" t="s">
-        <v>640</v>
-      </c>
-      <c r="C263" s="5" t="s">
-        <v>641</v>
-      </c>
-      <c r="D263" s="5" t="s">
-        <v>642</v>
-      </c>
-      <c r="E263" s="5" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="264" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A264" s="4">
-        <v>261</v>
-      </c>
-      <c r="B264" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="C264" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="D264" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="E264" s="3" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="265" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A265" s="4">
-        <v>262</v>
-      </c>
-      <c r="B265" s="5" t="s">
-        <v>647</v>
-      </c>
-      <c r="C265" s="5" t="s">
-        <v>648</v>
-      </c>
-      <c r="D265" s="5" t="s">
-        <v>649</v>
-      </c>
-      <c r="E265" s="5" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="266" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A266" s="4">
-        <v>263</v>
-      </c>
-      <c r="B266" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="C266" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="D266" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="E266" s="3" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="267" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A267" s="4">
-        <v>264</v>
-      </c>
-      <c r="B267" s="5" t="s">
-        <v>655</v>
-      </c>
-      <c r="C267" s="5" t="s">
-        <v>656</v>
-      </c>
-      <c r="D267" s="5" t="s">
-        <v>657</v>
-      </c>
-      <c r="E267" s="5" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="268" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A268" s="4">
-        <v>265</v>
-      </c>
-      <c r="B268" s="3" t="s">
-        <v>658</v>
-      </c>
-      <c r="C268" s="3" t="s">
-        <v>659</v>
-      </c>
-      <c r="D268" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="E268" s="3" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="269" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A269" s="4">
-        <v>266</v>
-      </c>
-      <c r="B269" s="5" t="s">
-        <v>660</v>
-      </c>
-      <c r="C269" s="5" t="s">
-        <v>661</v>
-      </c>
-      <c r="D269" s="5" t="s">
-        <v>661</v>
-      </c>
-      <c r="E269" s="5" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="270" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A270" s="4">
-        <v>267</v>
-      </c>
-      <c r="B270" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="C270" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="D270" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="E270" s="3" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="271" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A271" s="4">
-        <v>268</v>
-      </c>
-      <c r="B271" s="5" t="s">
-        <v>666</v>
-      </c>
-      <c r="C271" s="5" t="s">
-        <v>667</v>
-      </c>
-      <c r="D271" s="5" t="s">
-        <v>668</v>
-      </c>
-      <c r="E271" s="5" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="272" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A272" s="4">
-        <v>269</v>
-      </c>
-      <c r="B272" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="C272" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D272" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="E272" s="3" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="273" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="4">
-        <v>270</v>
-      </c>
-      <c r="B273" s="5" t="s">
-        <v>673</v>
-      </c>
-      <c r="C273" s="5" t="s">
         <v>674</v>
-      </c>
-      <c r="D273" s="5" t="s">
-        <v>671</v>
-      </c>
-      <c r="E273" s="5" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="274" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A274" s="4">
-        <v>271</v>
-      </c>
-      <c r="B274" s="3" t="s">
-        <v>675</v>
-      </c>
-      <c r="C274" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D274" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="E274" s="3" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="275" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A275" s="4">
-        <v>272</v>
-      </c>
-      <c r="B275" s="5" t="s">
-        <v>677</v>
-      </c>
-      <c r="C275" s="5" t="s">
-        <v>678</v>
-      </c>
-      <c r="D275" s="5" t="s">
-        <v>679</v>
-      </c>
-      <c r="E275" s="5" t="s">
-        <v>672</v>
       </c>
     </row>
   </sheetData>

--- a/รายชื่อโรงพยาบาลและที่ตั้ง_แยกจังหวัด.xlsx
+++ b/รายชื่อโรงพยาบาลและที่ตั้ง_แยกจังหวัด.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Desktop\Download\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Desktop\Download\ทำเว็บแอพ เช็ค รพ.ประกันสังคม 2569\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC7D23F-F5C0-4C47-B8D3-084EC23B7A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CDB4BF-BE3D-4DC4-AD8B-572E99662C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,10 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="685">
-  <si>
-    <t>รายชื่อโรงพยาบาลและข้อมูลที่ตั้ง - รพ. กรุงเทพมหานคร</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="683">
   <si>
     <t>ลำดับ</t>
   </si>
@@ -387,9 +384,6 @@
   </si>
   <si>
     <t>รพ.ไอเอ็มเอช ธนบุรี</t>
-  </si>
-  <si>
-    <t>รายชื่อโรงพยาบาลและข้อมูลที่ตั้ง - รพ. ต่างจังหวัดและปริมณฑล</t>
   </si>
   <si>
     <t>รพ.กระบี่ (สธ)</t>
@@ -2082,20 +2076,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF1F497D"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2163,30 +2150,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2489,4716 +2472,4692 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="77" customWidth="1"/>
+    <col min="2" max="2" width="92.42578125" customWidth="1"/>
     <col min="3" max="3" width="39.5703125" customWidth="1"/>
-    <col min="4" max="4" width="37.42578125" customWidth="1"/>
-    <col min="5" max="5" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="5" max="5" width="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-    </row>
-    <row r="3" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>37</v>
-      </c>
       <c r="E15" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D46" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C51" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D51" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D51" s="5" t="s">
-        <v>109</v>
-      </c>
       <c r="E51" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
-        <v>49</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="4">
-        <v>50</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E225"/>
+  <dimension ref="A1:E223"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="92.42578125" customWidth="1"/>
-    <col min="3" max="3" width="33" customWidth="1"/>
+    <col min="3" max="3" width="39.5703125" customWidth="1"/>
     <col min="4" max="4" width="44" customWidth="1"/>
     <col min="5" max="5" width="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-    </row>
-    <row r="3" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="D2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>5</v>
+      <c r="B3" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>134</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>176</v>
+        <v>680</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>682</v>
+        <v>180</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>136</v>
+        <v>200</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D35" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="E35" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>214</v>
-      </c>
       <c r="E39" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>223</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>225</v>
-      </c>
       <c r="D45" s="5" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>228</v>
+        <v>155</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>157</v>
+        <v>237</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="E49" s="5" t="s">
         <v>235</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
+        <v>681</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E51" s="5" t="s">
         <v>241</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>683</v>
+        <v>249</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C54" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>248</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>252</v>
+        <v>134</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>136</v>
+        <v>263</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C58" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>261</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>265</v>
+        <v>134</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>136</v>
+        <v>265</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>270</v>
+        <v>134</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>271</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>136</v>
+        <v>276</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C65" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="E65" s="5" t="s">
         <v>274</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>278</v>
+        <v>134</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>136</v>
+        <v>284</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C73" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="E73" s="5" t="s">
         <v>294</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C76" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E76" s="3" t="s">
         <v>294</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B77" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="D77" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="C77" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>305</v>
-      </c>
       <c r="E77" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="E80" s="3" t="s">
         <v>310</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>314</v>
+        <v>134</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>136</v>
+        <v>326</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C87" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="E87" s="5" t="s">
         <v>328</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B89" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="D89" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="C89" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>336</v>
-      </c>
       <c r="E89" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>337</v>
       </c>
       <c r="C90" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E90" s="3" t="s">
         <v>328</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D92" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="C92" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>341</v>
-      </c>
       <c r="E92" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>342</v>
       </c>
       <c r="C93" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="E93" s="5" t="s">
         <v>328</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>343</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>344</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>347</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>356</v>
+        <v>151</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C101" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="E101" s="5" t="s">
         <v>358</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>153</v>
+        <v>364</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>364</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B107" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="E107" s="5" t="s">
         <v>373</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="D107" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B109" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="D109" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="C109" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="D109" s="5" t="s">
-        <v>380</v>
-      </c>
       <c r="E109" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C112" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E112" s="3" t="s">
         <v>385</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>398</v>
+        <v>134</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B119" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="D119" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="C119" s="5" t="s">
+      <c r="E119" s="5" t="s">
         <v>408</v>
-      </c>
-      <c r="D119" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="E119" s="5" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>416</v>
+        <v>134</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>136</v>
+        <v>424</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>136</v>
+        <v>428</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C126" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="E126" s="3" t="s">
         <v>426</v>
-      </c>
-      <c r="D126" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B127" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="D127" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="C127" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="D127" s="5" t="s">
-        <v>431</v>
-      </c>
       <c r="E127" s="5" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>436</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>454</v>
+        <v>134</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>136</v>
+        <v>465</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B140" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="D140" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="C140" s="3" t="s">
+      <c r="E140" s="3" t="s">
         <v>467</v>
-      </c>
-      <c r="D140" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="E140" s="3" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>470</v>
+        <v>682</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>684</v>
+        <v>475</v>
       </c>
       <c r="C143" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="D143" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="D143" s="5" t="s">
-        <v>468</v>
-      </c>
       <c r="E143" s="5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="4">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B146" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="E146" s="3" t="s">
         <v>479</v>
-      </c>
-      <c r="C146" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="D146" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="E146" s="3" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="4">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>483</v>
+        <v>151</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="4">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>153</v>
+        <v>488</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="4">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B151" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="E151" s="5" t="s">
         <v>489</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="D151" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="E151" s="5" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="4">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B156" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D156" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="C156" s="3" t="s">
+      <c r="E156" s="3" t="s">
         <v>504</v>
-      </c>
-      <c r="D156" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="E156" s="3" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>136</v>
+        <v>511</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="C164" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="E164" s="3" t="s">
         <v>527</v>
-      </c>
-      <c r="D164" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="E164" s="3" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="4">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B165" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="C165" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="C165" s="5" t="s">
-        <v>531</v>
-      </c>
       <c r="D165" s="5" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>533</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="4">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B169" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D169" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="E169" s="5" t="s">
         <v>539</v>
-      </c>
-      <c r="C169" s="5" t="s">
-        <v>540</v>
-      </c>
-      <c r="D169" s="5" t="s">
-        <v>540</v>
-      </c>
-      <c r="E169" s="5" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B170" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="D170" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="C170" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="D170" s="3" t="s">
-        <v>544</v>
-      </c>
       <c r="E170" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="4">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>124</v>
+        <v>546</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="4">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="4">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>554</v>
+        <v>122</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="4">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B177" s="5" t="s">
         <v>555</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>556</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>124</v>
+        <v>557</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>540</v>
+        <v>559</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>546</v>
+        <v>562</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>546</v>
+        <v>562</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>563</v>
+        <v>122</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>564</v>
+        <v>544</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="4">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="184" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>124</v>
+        <v>569</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>546</v>
+        <v>570</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>541</v>
+        <v>571</v>
       </c>
     </row>
     <row r="185" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="4">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>541</v>
+        <v>575</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C187" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="D187" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="E187" s="5" t="s">
         <v>575</v>
-      </c>
-      <c r="D187" s="5" t="s">
-        <v>576</v>
-      </c>
-      <c r="E187" s="5" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="189" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="4">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B189" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="D189" s="5" t="s">
         <v>580</v>
       </c>
-      <c r="C189" s="5" t="s">
-        <v>581</v>
-      </c>
-      <c r="D189" s="5" t="s">
-        <v>582</v>
-      </c>
       <c r="E189" s="5" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="191" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="4">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="193" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="4">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>576</v>
+        <v>592</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>577</v>
+        <v>591</v>
       </c>
     </row>
     <row r="194" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>577</v>
+        <v>595</v>
       </c>
     </row>
     <row r="195" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="4">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B196" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="E196" s="3" t="s">
         <v>595</v>
-      </c>
-      <c r="C196" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="D196" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="E196" s="3" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="197" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="4">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
     </row>
     <row r="199" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="4">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="201" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="4">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
     </row>
     <row r="203" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="4">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C203" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="D203" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="E203" s="5" t="s">
         <v>616</v>
-      </c>
-      <c r="D203" s="5" t="s">
-        <v>617</v>
-      </c>
-      <c r="E203" s="5" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
     </row>
     <row r="205" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="4">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>622</v>
+        <v>436</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="C206" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="E206" s="3" t="s">
         <v>624</v>
-      </c>
-      <c r="D206" s="3" t="s">
-        <v>625</v>
-      </c>
-      <c r="E206" s="3" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="207" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="4">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>438</v>
+        <v>631</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="208" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>630</v>
+        <v>134</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
     </row>
     <row r="209" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="4">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>625</v>
+        <v>636</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>626</v>
+        <v>637</v>
       </c>
     </row>
     <row r="210" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="211" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="4">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="212" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>136</v>
+        <v>645</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>639</v>
+        <v>622</v>
       </c>
     </row>
     <row r="213" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="4">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
     </row>
     <row r="214" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>624</v>
+        <v>654</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="4">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="216" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="C216" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="E216" s="3" t="s">
         <v>654</v>
-      </c>
-      <c r="D216" s="3" t="s">
-        <v>655</v>
-      </c>
-      <c r="E216" s="3" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="217" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="4">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="218" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
     </row>
     <row r="219" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="4">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>656</v>
+        <v>669</v>
       </c>
     </row>
     <row r="220" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>665</v>
+        <v>175</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
     </row>
     <row r="221" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="222" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B222" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="E222" s="3" t="s">
         <v>672</v>
-      </c>
-      <c r="C222" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D222" s="3" t="s">
-        <v>673</v>
-      </c>
-      <c r="E222" s="3" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="223" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="4">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A224" s="2">
-        <v>221</v>
-      </c>
-      <c r="B224" s="3" t="s">
-        <v>677</v>
-      </c>
-      <c r="C224" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D224" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="E224" s="3" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A225" s="4">
-        <v>222</v>
-      </c>
-      <c r="B225" s="5" t="s">
-        <v>679</v>
-      </c>
-      <c r="C225" s="5" t="s">
-        <v>680</v>
-      </c>
-      <c r="D225" s="5" t="s">
-        <v>681</v>
-      </c>
-      <c r="E225" s="5" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/รายชื่อโรงพยาบาลและที่ตั้ง_แยกจังหวัด.xlsx
+++ b/รายชื่อโรงพยาบาลและที่ตั้ง_แยกจังหวัด.xlsx
@@ -8,20 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Desktop\Download\ทำเว็บแอพ เช็ค รพ.ประกันสังคม 2569\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CDB4BF-BE3D-4DC4-AD8B-572E99662C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7165B331-A038-4BDF-BB7D-EE41F5F02C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="รพ. กรุงเทพมหานคร" sheetId="1" r:id="rId1"/>
     <sheet name="รพ. ต่างจังหวัดและปริมณฑล" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="685">
   <si>
     <t>ลำดับ</t>
   </si>
@@ -2070,6 +2083,12 @@
   </si>
   <si>
     <t>รพ.เฉลิมพระเกียรติสมเด็จพระเทพรัตนราชสุดาฯ สยามบรมราชกุมารี ระยอง (สธ)</t>
+  </si>
+  <si>
+    <t>latitude</t>
+  </si>
+  <si>
+    <t>longitude</t>
   </si>
 </sst>
 </file>
@@ -2472,7 +2491,1198 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:G51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="92.42578125" customWidth="1"/>
+    <col min="3" max="3" width="39.5703125" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="5" max="5" width="33" customWidth="1"/>
+    <col min="6" max="7" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>13.7744</v>
+      </c>
+      <c r="G2">
+        <v>100.50830000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>13.7486</v>
+      </c>
+      <c r="G3">
+        <v>100.5097</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4">
+        <v>13.7323</v>
+      </c>
+      <c r="G4">
+        <v>100.5372</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>13.6989</v>
+      </c>
+      <c r="G5">
+        <v>100.4939</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>13.8797</v>
+      </c>
+      <c r="G6">
+        <v>100.5735</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <v>13.729699999999999</v>
+      </c>
+      <c r="G7">
+        <v>100.51009999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8">
+        <v>13.7441</v>
+      </c>
+      <c r="G8">
+        <v>100.53830000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9">
+        <v>13.847099999999999</v>
+      </c>
+      <c r="G9">
+        <v>100.5638</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10">
+        <v>13.818099999999999</v>
+      </c>
+      <c r="G10">
+        <v>100.6756</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11">
+        <v>13.666700000000001</v>
+      </c>
+      <c r="G11">
+        <v>100.38120000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12">
+        <v>13.5654</v>
+      </c>
+      <c r="G12">
+        <v>100.41370000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13">
+        <v>13.7667</v>
+      </c>
+      <c r="G13">
+        <v>100.5361</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14">
+        <v>13.908899999999999</v>
+      </c>
+      <c r="G14">
+        <v>100.6125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15">
+        <v>13.765000000000001</v>
+      </c>
+      <c r="G15">
+        <v>100.53749999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16">
+        <v>13.766299999999999</v>
+      </c>
+      <c r="G16">
+        <v>100.52549999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17">
+        <v>13.6922</v>
+      </c>
+      <c r="G17">
+        <v>100.37130000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18">
+        <v>13.7224</v>
+      </c>
+      <c r="G18">
+        <v>100.51860000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19">
+        <v>13.8569</v>
+      </c>
+      <c r="G19">
+        <v>100.8642</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20">
+        <v>13.7554</v>
+      </c>
+      <c r="G20">
+        <v>100.4851</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21">
+        <v>13.7081</v>
+      </c>
+      <c r="G21">
+        <v>100.4858</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22">
+        <v>13.7196</v>
+      </c>
+      <c r="G22">
+        <v>100.6979</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23">
+        <v>13.655799999999999</v>
+      </c>
+      <c r="G23">
+        <v>100.3164</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24">
+        <v>13.7121</v>
+      </c>
+      <c r="G24">
+        <v>100.58329999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25">
+        <v>13.7118</v>
+      </c>
+      <c r="G25">
+        <v>100.3929</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26">
+        <v>13.8291</v>
+      </c>
+      <c r="G26">
+        <v>100.54219999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27">
+        <v>13.766299999999999</v>
+      </c>
+      <c r="G27">
+        <v>100.6653</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28">
+        <v>13.813599999999999</v>
+      </c>
+      <c r="G28">
+        <v>100.7208</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29">
+        <v>13.814299999999999</v>
+      </c>
+      <c r="G29">
+        <v>100.7214</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30">
+        <v>13.666399999999999</v>
+      </c>
+      <c r="G30">
+        <v>100.6433</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31">
+        <v>13.6578</v>
+      </c>
+      <c r="G31">
+        <v>100.39530000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32">
+        <v>13.725</v>
+      </c>
+      <c r="G32">
+        <v>100.4611</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33">
+        <v>13.6769</v>
+      </c>
+      <c r="G33">
+        <v>100.4619</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34">
+        <v>13.923400000000001</v>
+      </c>
+      <c r="G34">
+        <v>100.6225</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <v>34</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35">
+        <v>13.801600000000001</v>
+      </c>
+      <c r="G35">
+        <v>100.5936</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36">
+        <v>13.8347</v>
+      </c>
+      <c r="G36">
+        <v>100.5744</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
+        <v>36</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37">
+        <v>13.664999999999999</v>
+      </c>
+      <c r="G37">
+        <v>100.4439</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38">
+        <v>13.823600000000001</v>
+      </c>
+      <c r="G38">
+        <v>100.66249999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
+        <v>38</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39">
+        <v>13.714399999999999</v>
+      </c>
+      <c r="G39">
+        <v>100.4456</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40">
+        <v>13.745799999999999</v>
+      </c>
+      <c r="G40">
+        <v>100.6019</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="4">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41">
+        <v>13.7461</v>
+      </c>
+      <c r="G41">
+        <v>100.6022</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42">
+        <v>13.7247</v>
+      </c>
+      <c r="G42">
+        <v>100.5217</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
+        <v>42</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43">
+        <v>13.888299999999999</v>
+      </c>
+      <c r="G43">
+        <v>100.5639</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44">
+        <v>13.7578</v>
+      </c>
+      <c r="G44">
+        <v>100.51860000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="4">
+        <v>44</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45">
+        <v>13.6823</v>
+      </c>
+      <c r="G45">
+        <v>100.505</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46">
+        <v>13.791499999999999</v>
+      </c>
+      <c r="G46">
+        <v>100.60939999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="4">
+        <v>46</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47">
+        <v>13.7356</v>
+      </c>
+      <c r="G47">
+        <v>100.6444</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48">
+        <v>13.655099999999999</v>
+      </c>
+      <c r="G48">
+        <v>100.64749999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="4">
+        <v>48</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49">
+        <v>13.6823</v>
+      </c>
+      <c r="G49">
+        <v>100.505</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50">
+        <v>13.749700000000001</v>
+      </c>
+      <c r="G50">
+        <v>100.51690000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="4">
+        <v>50</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51">
+        <v>13.715</v>
+      </c>
+      <c r="G51">
+        <v>100.47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G223"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2482,1745 +3692,1161 @@
     <col min="5" max="5" width="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F1" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6</v>
+        <v>122</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>7</v>
+        <v>123</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+      <c r="F2">
+        <v>8.0609999999999999</v>
+      </c>
+      <c r="G2">
+        <v>98.918499999999995</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>9</v>
+        <v>125</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>126</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>11</v>
+        <v>127</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+      <c r="F3">
+        <v>14.0413</v>
+      </c>
+      <c r="G3">
+        <v>99.789100000000005</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>12</v>
+        <v>129</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>13</v>
+        <v>130</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>13</v>
+        <v>127</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+      <c r="F4">
+        <v>14.053100000000001</v>
+      </c>
+      <c r="G4">
+        <v>99.812399999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+      <c r="F5">
+        <v>13.9785</v>
+      </c>
+      <c r="G5">
+        <v>99.645700000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>16</v>
+        <v>133</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="F6">
+        <v>16.434699999999999</v>
+      </c>
+      <c r="G6">
+        <v>103.5042</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="F7">
+        <v>16.4862</v>
+      </c>
+      <c r="G7">
+        <v>99.524100000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>22</v>
+        <v>140</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>13</v>
+        <v>134</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>13</v>
+        <v>141</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="F8">
+        <v>16.435700000000001</v>
+      </c>
+      <c r="G8">
+        <v>102.8339</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>25</v>
+        <v>144</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="F9">
+        <v>16.5444</v>
+      </c>
+      <c r="G9">
+        <v>102.5532</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>27</v>
+        <v>141</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="F10">
+        <v>16.467099999999999</v>
+      </c>
+      <c r="G10">
+        <v>102.82510000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>29</v>
+        <v>147</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>30</v>
+        <v>148</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="F11">
+        <v>12.637499999999999</v>
+      </c>
+      <c r="G11">
+        <v>101.1542</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>31</v>
+        <v>150</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>32</v>
+        <v>151</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>33</v>
+        <v>152</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+      <c r="F12">
+        <v>13.6843</v>
+      </c>
+      <c r="G12">
+        <v>101.07429999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>34</v>
+        <v>154</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>35</v>
+        <v>155</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>36</v>
+        <v>152</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+      <c r="F13">
+        <v>13.687200000000001</v>
+      </c>
+      <c r="G13">
+        <v>101.0821</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>37</v>
+        <v>156</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>38</v>
+        <v>157</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>39</v>
+        <v>158</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+      <c r="F14">
+        <v>13.5671</v>
+      </c>
+      <c r="G14">
+        <v>101.0543</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>36</v>
+        <v>161</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="F15">
+        <v>13.3614</v>
+      </c>
+      <c r="G15">
+        <v>100.9845</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>41</v>
+        <v>163</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>35</v>
+        <v>164</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>36</v>
+        <v>165</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="F16">
+        <v>12.9236</v>
+      </c>
+      <c r="G16">
+        <v>100.90779999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>43</v>
+        <v>167</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>44</v>
+        <v>167</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="F17">
+        <v>13.4475</v>
+      </c>
+      <c r="G17">
+        <v>101.1234</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>46</v>
+        <v>169</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="F18">
+        <v>12.721399999999999</v>
+      </c>
+      <c r="G18">
+        <v>100.9123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>48</v>
+        <v>171</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>49</v>
+        <v>172</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>50</v>
+        <v>172</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="F19">
+        <v>13.176399999999999</v>
+      </c>
+      <c r="G19">
+        <v>100.9234</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>51</v>
+        <v>173</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>53</v>
+        <v>165</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="F20">
+        <v>12.934799999999999</v>
+      </c>
+      <c r="G20">
+        <v>100.8901</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>54</v>
+        <v>174</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>55</v>
+        <v>175</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="F21">
+        <v>13.2842</v>
+      </c>
+      <c r="G21">
+        <v>100.9145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>57</v>
+        <v>176</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>58</v>
+        <v>177</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>58</v>
+        <v>172</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="F22">
+        <v>13.064500000000001</v>
+      </c>
+      <c r="G22">
+        <v>101.0856</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>59</v>
+        <v>680</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>60</v>
+        <v>178</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="F23">
+        <v>13.0768</v>
+      </c>
+      <c r="G23">
+        <v>100.9156</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>61</v>
+        <v>179</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>62</v>
+        <v>172</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>63</v>
+        <v>172</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="F24">
+        <v>13.1678</v>
+      </c>
+      <c r="G24">
+        <v>100.9256</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>64</v>
+        <v>180</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>65</v>
+        <v>178</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>44</v>
+        <v>172</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="F25">
+        <v>13.0754</v>
+      </c>
+      <c r="G25">
+        <v>100.9156</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>66</v>
+        <v>181</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>67</v>
+        <v>182</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>68</v>
+        <v>161</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="F26">
+        <v>13.424300000000001</v>
+      </c>
+      <c r="G26">
+        <v>101.03449999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>69</v>
+        <v>183</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>70</v>
+        <v>184</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>70</v>
+        <v>161</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="F27">
+        <v>13.313499999999999</v>
+      </c>
+      <c r="G27">
+        <v>100.96339999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>71</v>
+        <v>185</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>72</v>
+        <v>172</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="F28">
+        <v>13.17</v>
+      </c>
+      <c r="G28">
+        <v>100.9345</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>72</v>
+        <v>177</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>72</v>
+        <v>172</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="F29">
+        <v>13.061199999999999</v>
+      </c>
+      <c r="G29">
+        <v>101.05670000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>76</v>
+        <v>190</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+      <c r="F30">
+        <v>15.0844</v>
+      </c>
+      <c r="G30">
+        <v>100.12560000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>29</v>
+        <v>134</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>30</v>
+        <v>193</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+      <c r="F31">
+        <v>15.803699999999999</v>
+      </c>
+      <c r="G31">
+        <v>102.04349999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>79</v>
+        <v>196</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+      <c r="F32">
+        <v>10.4908</v>
+      </c>
+      <c r="G32">
+        <v>99.1678</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>81</v>
+        <v>199</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>83</v>
+        <v>201</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+      <c r="F33">
+        <v>19.907699999999998</v>
+      </c>
+      <c r="G33">
+        <v>99.832899999999995</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>84</v>
+        <v>203</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>39</v>
+        <v>204</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>39</v>
+        <v>201</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+      <c r="F34">
+        <v>19.9238</v>
+      </c>
+      <c r="G34">
+        <v>99.834500000000006</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>85</v>
+        <v>205</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>86</v>
+        <v>200</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>86</v>
+        <v>201</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+      <c r="F35">
+        <v>19.921299999999999</v>
+      </c>
+      <c r="G35">
+        <v>99.845600000000005</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>87</v>
+        <v>206</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>88</v>
+        <v>207</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>25</v>
+        <v>208</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+      <c r="F36">
+        <v>18.8354</v>
+      </c>
+      <c r="G36">
+        <v>98.974500000000006</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>89</v>
+        <v>210</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>33</v>
+        <v>212</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+      <c r="F37">
+        <v>18.784500000000001</v>
+      </c>
+      <c r="G37">
+        <v>98.967799999999997</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>91</v>
+        <v>213</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>92</v>
+        <v>214</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>93</v>
+        <v>215</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+      <c r="F38">
+        <v>18.591200000000001</v>
+      </c>
+      <c r="G38">
+        <v>98.764499999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>94</v>
+        <v>216</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>95</v>
+        <v>217</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>80</v>
+        <v>212</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+      <c r="F39">
+        <v>18.761199999999999</v>
+      </c>
+      <c r="G39">
+        <v>98.956699999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>96</v>
+        <v>218</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>97</v>
+        <v>219</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>98</v>
+        <v>212</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+      <c r="F40">
+        <v>18.814299999999999</v>
+      </c>
+      <c r="G40">
+        <v>98.995599999999996</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>99</v>
+        <v>220</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>97</v>
+        <v>221</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>98</v>
+        <v>212</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+      <c r="F41">
+        <v>18.7956</v>
+      </c>
+      <c r="G41">
+        <v>98.967799999999997</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>100</v>
+        <v>222</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>101</v>
+        <v>223</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>47</v>
+        <v>212</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+      <c r="F42">
+        <v>18.8078</v>
+      </c>
+      <c r="G42">
+        <v>98.978899999999996</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>102</v>
+        <v>224</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>103</v>
+        <v>223</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>18</v>
+        <v>212</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+      <c r="F43">
+        <v>18.8156</v>
+      </c>
+      <c r="G43">
+        <v>98.981200000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>104</v>
+        <v>225</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>105</v>
+        <v>226</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>7</v>
+        <v>227</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+      <c r="F44">
+        <v>7.5622999999999996</v>
+      </c>
+      <c r="G44">
+        <v>99.612300000000005</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>106</v>
+        <v>229</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>107</v>
+        <v>226</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>108</v>
+        <v>227</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+      <c r="F45">
+        <v>7.5589000000000004</v>
+      </c>
+      <c r="G45">
+        <v>99.605599999999995</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>109</v>
+        <v>230</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>111</v>
+        <v>231</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+      <c r="F46">
+        <v>12.2478</v>
+      </c>
+      <c r="G46">
+        <v>102.5123</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>112</v>
+        <v>233</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>113</v>
+        <v>234</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>114</v>
+        <v>234</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+      <c r="F47">
+        <v>16.715399999999999</v>
+      </c>
+      <c r="G47">
+        <v>98.567800000000005</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>115</v>
+        <v>236</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>116</v>
+        <v>237</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>76</v>
+        <v>238</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+      <c r="F48">
+        <v>16.698699999999999</v>
+      </c>
+      <c r="G48">
+        <v>98.556700000000006</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>117</v>
+        <v>239</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>107</v>
+        <v>234</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>108</v>
+        <v>234</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+      <c r="F49">
+        <v>16.721399999999999</v>
+      </c>
+      <c r="G49">
+        <v>98.578900000000004</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>118</v>
+        <v>240</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>119</v>
+        <v>241</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>11</v>
+        <v>242</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+      <c r="F50">
+        <v>14.2089</v>
+      </c>
+      <c r="G50">
+        <v>101.1678</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E223"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="92.42578125" customWidth="1"/>
-    <col min="3" max="3" width="39.5703125" customWidth="1"/>
-    <col min="4" max="4" width="44" customWidth="1"/>
-    <col min="5" max="5" width="33" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
-        <v>18</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>19</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
-        <v>20</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
-        <v>21</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
-        <v>22</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>680</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
-        <v>23</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
-        <v>24</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
-        <v>25</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
-        <v>26</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
-        <v>27</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
-        <v>28</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
-        <v>29</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="4">
-        <v>30</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
-        <v>31</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
-        <v>32</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
-        <v>33</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="4">
-        <v>34</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
-        <v>35</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="4">
-        <v>36</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
-        <v>37</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="4">
-        <v>38</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
-        <v>39</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="4">
-        <v>40</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
-        <v>41</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="4">
-        <v>42</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
-        <v>43</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="4">
-        <v>44</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
-        <v>45</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="4">
-        <v>46</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
-        <v>47</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="4">
-        <v>48</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
-        <v>49</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="4">
-        <v>50</v>
-      </c>
-      <c r="B51" s="5" t="s">
         <v>681</v>
       </c>
       <c r="C51" s="5" t="s">
@@ -4232,8 +4858,14 @@
       <c r="E51" s="5" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F51">
+        <v>14.2156</v>
+      </c>
+      <c r="G51">
+        <v>101.1789</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -4249,8 +4881,14 @@
       <c r="E52" s="3" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F52">
+        <v>14.0754</v>
+      </c>
+      <c r="G52">
+        <v>100.65430000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -4266,8 +4904,14 @@
       <c r="E53" s="5" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F53">
+        <v>13.819699999999999</v>
+      </c>
+      <c r="G53">
+        <v>100.0634</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -4283,8 +4927,14 @@
       <c r="E54" s="3" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F54">
+        <v>13.7385</v>
+      </c>
+      <c r="G54">
+        <v>100.2543</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -4300,8 +4950,14 @@
       <c r="E55" s="5" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F55">
+        <v>17.4116</v>
+      </c>
+      <c r="G55">
+        <v>104.7865</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -4317,8 +4973,14 @@
       <c r="E56" s="3" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F56">
+        <v>14.945600000000001</v>
+      </c>
+      <c r="G56">
+        <v>102.04559999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -4334,8 +4996,14 @@
       <c r="E57" s="5" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F57">
+        <v>14.9785</v>
+      </c>
+      <c r="G57">
+        <v>102.1054</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -4351,8 +5019,14 @@
       <c r="E58" s="3" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F58">
+        <v>14.6854</v>
+      </c>
+      <c r="G58">
+        <v>101.38760000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -4368,8 +5042,14 @@
       <c r="E59" s="5" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F59">
+        <v>14.9781</v>
+      </c>
+      <c r="G59">
+        <v>102.0945</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -4385,8 +5065,14 @@
       <c r="E60" s="3" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F60">
+        <v>14.882099999999999</v>
+      </c>
+      <c r="G60">
+        <v>102.0234</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -4402,8 +5088,14 @@
       <c r="E61" s="5" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F61">
+        <v>14.715400000000001</v>
+      </c>
+      <c r="G61">
+        <v>101.4054</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -4419,8 +5111,14 @@
       <c r="E62" s="3" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F62">
+        <v>14.9754</v>
+      </c>
+      <c r="G62">
+        <v>102.0912</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -4436,8 +5134,14 @@
       <c r="E63" s="5" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F63">
+        <v>8.4412000000000003</v>
+      </c>
+      <c r="G63">
+        <v>99.9876</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -4453,8 +5157,14 @@
       <c r="E64" s="3" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F64">
+        <v>8.1677999999999997</v>
+      </c>
+      <c r="G64">
+        <v>99.954300000000003</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -4470,8 +5180,14 @@
       <c r="E65" s="5" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F65">
+        <v>8.6542999999999992</v>
+      </c>
+      <c r="G65">
+        <v>99.912300000000002</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -4487,8 +5203,14 @@
       <c r="E66" s="3" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F66">
+        <v>8.4123000000000001</v>
+      </c>
+      <c r="G66">
+        <v>99.976500000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -4504,8 +5226,14 @@
       <c r="E67" s="5" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F67">
+        <v>9.0764999999999993</v>
+      </c>
+      <c r="G67">
+        <v>99.897599999999997</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -4521,8 +5249,14 @@
       <c r="E68" s="3" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F68">
+        <v>8.6432000000000002</v>
+      </c>
+      <c r="G68">
+        <v>99.876499999999993</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -4538,8 +5272,14 @@
       <c r="E69" s="5" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F69">
+        <v>15.712300000000001</v>
+      </c>
+      <c r="G69">
+        <v>100.1234</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -4555,8 +5295,14 @@
       <c r="E70" s="3" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F70">
+        <v>15.6876</v>
+      </c>
+      <c r="G70">
+        <v>100.10980000000001</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -4572,8 +5318,14 @@
       <c r="E71" s="5" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F71">
+        <v>13.8965</v>
+      </c>
+      <c r="G71">
+        <v>100.5234</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -4589,8 +5341,14 @@
       <c r="E72" s="3" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F72">
+        <v>13.873200000000001</v>
+      </c>
+      <c r="G72">
+        <v>100.4876</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -4606,8 +5364,14 @@
       <c r="E73" s="5" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F73">
+        <v>13.8645</v>
+      </c>
+      <c r="G73">
+        <v>100.5123</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -4623,8 +5387,14 @@
       <c r="E74" s="3" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F74">
+        <v>13.882099999999999</v>
+      </c>
+      <c r="G74">
+        <v>100.4987</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -4640,8 +5410,14 @@
       <c r="E75" s="5" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F75">
+        <v>13.8743</v>
+      </c>
+      <c r="G75">
+        <v>100.4567</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -4657,8 +5433,14 @@
       <c r="E76" s="3" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F76">
+        <v>13.9123</v>
+      </c>
+      <c r="G76">
+        <v>100.5123</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -4674,8 +5456,14 @@
       <c r="E77" s="5" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F77">
+        <v>13.9245</v>
+      </c>
+      <c r="G77">
+        <v>100.43210000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -4691,8 +5479,14 @@
       <c r="E78" s="3" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F78">
+        <v>6.4356</v>
+      </c>
+      <c r="G78">
+        <v>101.81229999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -4708,8 +5502,14 @@
       <c r="E79" s="5" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F79">
+        <v>6.0354000000000001</v>
+      </c>
+      <c r="G79">
+        <v>101.9678</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -4725,8 +5525,14 @@
       <c r="E80" s="3" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F80">
+        <v>6.4253999999999998</v>
+      </c>
+      <c r="G80">
+        <v>101.81229999999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -4742,8 +5548,14 @@
       <c r="E81" s="5" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F81">
+        <v>18.784500000000001</v>
+      </c>
+      <c r="G81">
+        <v>100.77889999999999</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -4759,8 +5571,14 @@
       <c r="E82" s="3" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F82">
+        <v>14.6432</v>
+      </c>
+      <c r="G82">
+        <v>102.7765</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -4776,8 +5594,14 @@
       <c r="E83" s="5" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F83">
+        <v>14.9876</v>
+      </c>
+      <c r="G83">
+        <v>103.1123</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -4793,8 +5617,14 @@
       <c r="E84" s="3" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F84">
+        <v>18.3567</v>
+      </c>
+      <c r="G84">
+        <v>103.65430000000001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -4810,8 +5640,14 @@
       <c r="E85" s="5" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F85">
+        <v>14.076499999999999</v>
+      </c>
+      <c r="G85">
+        <v>100.60980000000001</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -4827,8 +5663,14 @@
       <c r="E86" s="3" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F86">
+        <v>14.035399999999999</v>
+      </c>
+      <c r="G86">
+        <v>100.5234</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -4844,8 +5686,14 @@
       <c r="E87" s="5" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F87">
+        <v>14.0543</v>
+      </c>
+      <c r="G87">
+        <v>100.6045</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -4861,8 +5709,14 @@
       <c r="E88" s="3" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F88">
+        <v>14.0123</v>
+      </c>
+      <c r="G88">
+        <v>100.6123</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -4878,8 +5732,14 @@
       <c r="E89" s="5" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F89">
+        <v>14.0245</v>
+      </c>
+      <c r="G89">
+        <v>100.60760000000001</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -4895,8 +5755,14 @@
       <c r="E90" s="3" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F90">
+        <v>13.9876</v>
+      </c>
+      <c r="G90">
+        <v>100.6187</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -4912,8 +5778,14 @@
       <c r="E91" s="5" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F91">
+        <v>14.043200000000001</v>
+      </c>
+      <c r="G91">
+        <v>100.6234</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -4929,8 +5801,14 @@
       <c r="E92" s="3" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F92">
+        <v>13.9765</v>
+      </c>
+      <c r="G92">
+        <v>100.6345</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -4946,8 +5824,14 @@
       <c r="E93" s="5" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F93">
+        <v>14.0321</v>
+      </c>
+      <c r="G93">
+        <v>100.6056</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -4963,8 +5847,14 @@
       <c r="E94" s="3" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F94">
+        <v>14.0456</v>
+      </c>
+      <c r="G94">
+        <v>100.6123</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -4980,8 +5870,14 @@
       <c r="E95" s="5" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F95">
+        <v>11.8345</v>
+      </c>
+      <c r="G95">
+        <v>99.512299999999996</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -4997,8 +5893,14 @@
       <c r="E96" s="3" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F96">
+        <v>11.212300000000001</v>
+      </c>
+      <c r="G96">
+        <v>99.812299999999993</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
         <v>96</v>
       </c>
@@ -5014,8 +5916,14 @@
       <c r="E97" s="5" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F97">
+        <v>11.8156</v>
+      </c>
+      <c r="G97">
+        <v>99.798699999999997</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -5031,8 +5939,14 @@
       <c r="E98" s="3" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F98">
+        <v>12.5532</v>
+      </c>
+      <c r="G98">
+        <v>99.954300000000003</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
         <v>98</v>
       </c>
@@ -5048,8 +5962,14 @@
       <c r="E99" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F99">
+        <v>13.9876</v>
+      </c>
+      <c r="G99">
+        <v>101.7345</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -5065,8 +5985,14 @@
       <c r="E100" s="3" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F100">
+        <v>14.156700000000001</v>
+      </c>
+      <c r="G100">
+        <v>101.3789</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -5082,8 +6008,14 @@
       <c r="E101" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F101">
+        <v>14.0678</v>
+      </c>
+      <c r="G101">
+        <v>101.37560000000001</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -5099,8 +6031,14 @@
       <c r="E102" s="3" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F102">
+        <v>13.9876</v>
+      </c>
+      <c r="G102">
+        <v>101.56780000000001</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -5116,8 +6054,14 @@
       <c r="E103" s="5" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F103">
+        <v>14.056699999999999</v>
+      </c>
+      <c r="G103">
+        <v>101.3789</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -5133,8 +6077,14 @@
       <c r="E104" s="3" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F104">
+        <v>6.8788999999999998</v>
+      </c>
+      <c r="G104">
+        <v>101.4876</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -5150,8 +6100,14 @@
       <c r="E105" s="5" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F105">
+        <v>14.3543</v>
+      </c>
+      <c r="G105">
+        <v>100.56780000000001</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>105</v>
       </c>
@@ -5167,8 +6123,14 @@
       <c r="E106" s="3" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="107" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F106">
+        <v>14.2432</v>
+      </c>
+      <c r="G106">
+        <v>100.32340000000001</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
         <v>106</v>
       </c>
@@ -5184,8 +6146,14 @@
       <c r="E107" s="5" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="108" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F107">
+        <v>14.345599999999999</v>
+      </c>
+      <c r="G107">
+        <v>100.6123</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>107</v>
       </c>
@@ -5201,8 +6169,14 @@
       <c r="E108" s="3" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="109" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F108">
+        <v>14.332100000000001</v>
+      </c>
+      <c r="G108">
+        <v>100.58759999999999</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
         <v>108</v>
       </c>
@@ -5218,8 +6192,14 @@
       <c r="E109" s="5" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="110" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F109">
+        <v>14.321</v>
+      </c>
+      <c r="G109">
+        <v>100.6345</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>109</v>
       </c>
@@ -5235,8 +6215,14 @@
       <c r="E110" s="3" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="111" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F110">
+        <v>19.523399999999999</v>
+      </c>
+      <c r="G110">
+        <v>100.3456</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
         <v>110</v>
       </c>
@@ -5252,8 +6238,14 @@
       <c r="E111" s="5" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="112" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F111">
+        <v>19.1678</v>
+      </c>
+      <c r="G111">
+        <v>100.1789</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>111</v>
       </c>
@@ -5269,8 +6261,14 @@
       <c r="E112" s="3" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="113" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F112">
+        <v>19.034500000000001</v>
+      </c>
+      <c r="G112">
+        <v>100.2012</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
         <v>112</v>
       </c>
@@ -5286,8 +6284,14 @@
       <c r="E113" s="5" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F113">
+        <v>8.8233999999999995</v>
+      </c>
+      <c r="G113">
+        <v>98.378900000000002</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>113</v>
       </c>
@@ -5303,8 +6307,14 @@
       <c r="E114" s="3" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="115" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F114">
+        <v>8.4456000000000007</v>
+      </c>
+      <c r="G114">
+        <v>98.512299999999996</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
         <v>114</v>
       </c>
@@ -5320,8 +6330,14 @@
       <c r="E115" s="5" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="116" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F115">
+        <v>7.6123000000000003</v>
+      </c>
+      <c r="G115">
+        <v>99.812299999999993</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>115</v>
       </c>
@@ -5337,8 +6353,14 @@
       <c r="E116" s="3" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="117" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F116">
+        <v>16.443200000000001</v>
+      </c>
+      <c r="G116">
+        <v>100.3456</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
         <v>116</v>
       </c>
@@ -5354,8 +6376,14 @@
       <c r="E117" s="5" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="118" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F117">
+        <v>16.823399999999999</v>
+      </c>
+      <c r="G117">
+        <v>100.26779999999999</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>117</v>
       </c>
@@ -5371,8 +6399,14 @@
       <c r="E118" s="3" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="119" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F118">
+        <v>16.8123</v>
+      </c>
+      <c r="G118">
+        <v>100.2567</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
         <v>118</v>
       </c>
@@ -5388,8 +6422,14 @@
       <c r="E119" s="5" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="120" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F119">
+        <v>16.7456</v>
+      </c>
+      <c r="G119">
+        <v>100.2123</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>119</v>
       </c>
@@ -5405,8 +6445,14 @@
       <c r="E120" s="3" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F120">
+        <v>16.8123</v>
+      </c>
+      <c r="G120">
+        <v>100.26560000000001</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
         <v>120</v>
       </c>
@@ -5422,8 +6468,14 @@
       <c r="E121" s="5" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="122" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F121">
+        <v>13.112299999999999</v>
+      </c>
+      <c r="G121">
+        <v>99.954300000000003</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>121</v>
       </c>
@@ -5439,8 +6491,14 @@
       <c r="E122" s="3" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="123" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F122">
+        <v>16.423400000000001</v>
+      </c>
+      <c r="G122">
+        <v>101.1678</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
         <v>122</v>
       </c>
@@ -5456,8 +6514,14 @@
       <c r="E123" s="5" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="124" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F123">
+        <v>18.145600000000002</v>
+      </c>
+      <c r="G123">
+        <v>100.1456</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>123</v>
       </c>
@@ -5473,8 +6537,14 @@
       <c r="E124" s="3" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="125" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F124">
+        <v>7.8922999999999996</v>
+      </c>
+      <c r="G124">
+        <v>98.298699999999997</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
         <v>124</v>
       </c>
@@ -5490,8 +6560,14 @@
       <c r="E125" s="5" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="126" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F125">
+        <v>7.8822999999999999</v>
+      </c>
+      <c r="G125">
+        <v>98.397800000000004</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>125</v>
       </c>
@@ -5507,8 +6583,14 @@
       <c r="E126" s="3" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="127" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F126">
+        <v>7.8956</v>
+      </c>
+      <c r="G126">
+        <v>98.378900000000002</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
         <v>126</v>
       </c>
@@ -5524,8 +6606,14 @@
       <c r="E127" s="5" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="128" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F127">
+        <v>7.8912000000000004</v>
+      </c>
+      <c r="G127">
+        <v>98.398700000000005</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>127</v>
       </c>
@@ -5541,8 +6629,14 @@
       <c r="E128" s="3" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="129" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F128">
+        <v>7.8875999999999999</v>
+      </c>
+      <c r="G128">
+        <v>98.381200000000007</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
         <v>128</v>
       </c>
@@ -5558,8 +6652,14 @@
       <c r="E129" s="5" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="130" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F129">
+        <v>16.1876</v>
+      </c>
+      <c r="G129">
+        <v>103.2567</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>129</v>
       </c>
@@ -5575,8 +6675,14 @@
       <c r="E130" s="3" t="s">
         <v>438</v>
       </c>
-    </row>
-    <row r="131" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F130">
+        <v>16.198699999999999</v>
+      </c>
+      <c r="G130">
+        <v>103.26779999999999</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
         <v>130</v>
       </c>
@@ -5592,8 +6698,14 @@
       <c r="E131" s="5" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="132" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F131">
+        <v>16.534500000000001</v>
+      </c>
+      <c r="G131">
+        <v>104.53449999999999</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>131</v>
       </c>
@@ -5609,8 +6721,14 @@
       <c r="E132" s="3" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="133" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F132">
+        <v>18.234500000000001</v>
+      </c>
+      <c r="G132">
+        <v>100.1876</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
         <v>132</v>
       </c>
@@ -5626,8 +6744,14 @@
       <c r="E133" s="5" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="134" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F133">
+        <v>15.7987</v>
+      </c>
+      <c r="G133">
+        <v>104.5123</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>133</v>
       </c>
@@ -5643,8 +6767,14 @@
       <c r="E134" s="3" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="135" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F134">
+        <v>5.7765000000000004</v>
+      </c>
+      <c r="G134">
+        <v>101.06780000000001</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -5660,8 +6790,14 @@
       <c r="E135" s="5" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="136" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F135">
+        <v>6.5431999999999997</v>
+      </c>
+      <c r="G135">
+        <v>101.27889999999999</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>135</v>
       </c>
@@ -5677,8 +6813,14 @@
       <c r="E136" s="3" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="137" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F136">
+        <v>16.054300000000001</v>
+      </c>
+      <c r="G136">
+        <v>103.65430000000001</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
         <v>136</v>
       </c>
@@ -5694,8 +6836,14 @@
       <c r="E137" s="5" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="138" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F137">
+        <v>9.9678000000000004</v>
+      </c>
+      <c r="G137">
+        <v>98.634500000000003</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>137</v>
       </c>
@@ -5711,8 +6859,14 @@
       <c r="E138" s="3" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="139" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F138">
+        <v>12.678900000000001</v>
+      </c>
+      <c r="G138">
+        <v>101.2567</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -5728,8 +6882,14 @@
       <c r="E139" s="5" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="140" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F139">
+        <v>12.689</v>
+      </c>
+      <c r="G139">
+        <v>101.26779999999999</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>139</v>
       </c>
@@ -5745,8 +6905,14 @@
       <c r="E140" s="3" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="141" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F140">
+        <v>12.6912</v>
+      </c>
+      <c r="G140">
+        <v>101.2456</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -5762,8 +6928,14 @@
       <c r="E141" s="5" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F141">
+        <v>12.685600000000001</v>
+      </c>
+      <c r="G141">
+        <v>101.2345</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>141</v>
       </c>
@@ -5779,8 +6951,14 @@
       <c r="E142" s="3" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="143" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F142">
+        <v>12.9876</v>
+      </c>
+      <c r="G142">
+        <v>101.2123</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -5796,8 +6974,14 @@
       <c r="E143" s="5" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="144" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F143">
+        <v>12.978899999999999</v>
+      </c>
+      <c r="G143">
+        <v>101.2012</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>143</v>
       </c>
@@ -5813,8 +6997,14 @@
       <c r="E144" s="3" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="145" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F144">
+        <v>13.5678</v>
+      </c>
+      <c r="G144">
+        <v>99.878900000000002</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -5830,8 +7020,14 @@
       <c r="E145" s="5" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="146" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F145">
+        <v>13.8123</v>
+      </c>
+      <c r="G145">
+        <v>99.876499999999993</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>145</v>
       </c>
@@ -5847,8 +7043,14 @@
       <c r="E146" s="3" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="147" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F146">
+        <v>13.689</v>
+      </c>
+      <c r="G146">
+        <v>99.854299999999995</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="4">
         <v>146</v>
       </c>
@@ -5864,8 +7066,14 @@
       <c r="E147" s="5" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="148" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F147">
+        <v>13.5345</v>
+      </c>
+      <c r="G147">
+        <v>99.823400000000007</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>147</v>
       </c>
@@ -5881,8 +7089,14 @@
       <c r="E148" s="3" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="149" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F148">
+        <v>13.523400000000001</v>
+      </c>
+      <c r="G148">
+        <v>99.834500000000006</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="4">
         <v>148</v>
       </c>
@@ -5898,8 +7112,14 @@
       <c r="E149" s="5" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="150" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F149">
+        <v>15.0123</v>
+      </c>
+      <c r="G149">
+        <v>100.4876</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>149</v>
       </c>
@@ -5915,8 +7135,14 @@
       <c r="E150" s="3" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="151" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F150">
+        <v>14.802300000000001</v>
+      </c>
+      <c r="G150">
+        <v>100.6123</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="4">
         <v>150</v>
       </c>
@@ -5932,8 +7158,14 @@
       <c r="E151" s="5" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="152" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F151">
+        <v>14.7956</v>
+      </c>
+      <c r="G151">
+        <v>100.6234</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>151</v>
       </c>
@@ -5949,8 +7181,14 @@
       <c r="E152" s="3" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="153" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F152">
+        <v>18.285599999999999</v>
+      </c>
+      <c r="G152">
+        <v>99.489199999999997</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="4">
         <v>152</v>
       </c>
@@ -5966,8 +7204,14 @@
       <c r="E153" s="5" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="154" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F153">
+        <v>18.2789</v>
+      </c>
+      <c r="G153">
+        <v>99.497799999999998</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>153</v>
       </c>
@@ -5983,8 +7227,14 @@
       <c r="E154" s="3" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="155" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F154">
+        <v>18.571200000000001</v>
+      </c>
+      <c r="G154">
+        <v>99.012299999999996</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
         <v>154</v>
       </c>
@@ -6000,8 +7250,14 @@
       <c r="E155" s="5" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="156" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F155">
+        <v>18.581199999999999</v>
+      </c>
+      <c r="G155">
+        <v>99.023399999999995</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>155</v>
       </c>
@@ -6017,8 +7273,14 @@
       <c r="E156" s="3" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="157" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F156">
+        <v>18.576499999999999</v>
+      </c>
+      <c r="G156">
+        <v>99.015600000000006</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
         <v>156</v>
       </c>
@@ -6034,8 +7296,14 @@
       <c r="E157" s="5" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="158" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F157">
+        <v>18.584499999999998</v>
+      </c>
+      <c r="G157">
+        <v>99.021199999999993</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>157</v>
       </c>
@@ -6051,8 +7319,14 @@
       <c r="E158" s="3" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="159" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F158">
+        <v>17.4876</v>
+      </c>
+      <c r="G158">
+        <v>101.7345</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
         <v>158</v>
       </c>
@@ -6068,8 +7342,14 @@
       <c r="E159" s="5" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="160" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F159">
+        <v>15.112299999999999</v>
+      </c>
+      <c r="G159">
+        <v>104.3245</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>159</v>
       </c>
@@ -6085,8 +7365,14 @@
       <c r="E160" s="3" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="161" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F160">
+        <v>17.154299999999999</v>
+      </c>
+      <c r="G160">
+        <v>104.1456</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
         <v>160</v>
       </c>
@@ -6102,8 +7388,14 @@
       <c r="E161" s="5" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="162" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F161">
+        <v>17.476500000000001</v>
+      </c>
+      <c r="G161">
+        <v>103.7543</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>161</v>
       </c>
@@ -6119,8 +7411,14 @@
       <c r="E162" s="3" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="163" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F162">
+        <v>7.2012</v>
+      </c>
+      <c r="G162">
+        <v>100.59780000000001</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
         <v>162</v>
       </c>
@@ -6136,8 +7434,14 @@
       <c r="E163" s="5" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="164" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F163">
+        <v>7.0077999999999996</v>
+      </c>
+      <c r="G163">
+        <v>100.5012</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>163</v>
       </c>
@@ -6153,8 +7457,14 @@
       <c r="E164" s="3" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="165" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F164">
+        <v>6.9977999999999998</v>
+      </c>
+      <c r="G164">
+        <v>100.4789</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="4">
         <v>164</v>
       </c>
@@ -6170,8 +7480,14 @@
       <c r="E165" s="5" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="166" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F165">
+        <v>7.0011999999999999</v>
+      </c>
+      <c r="G165">
+        <v>100.48560000000001</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>165</v>
       </c>
@@ -6187,8 +7503,14 @@
       <c r="E166" s="3" t="s">
         <v>536</v>
       </c>
-    </row>
-    <row r="167" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F166">
+        <v>6.6234000000000002</v>
+      </c>
+      <c r="G166">
+        <v>100.06780000000001</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
         <v>166</v>
       </c>
@@ -6204,8 +7526,14 @@
       <c r="E167" s="5" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="168" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F167">
+        <v>13.5678</v>
+      </c>
+      <c r="G167">
+        <v>100.82340000000001</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
         <v>167</v>
       </c>
@@ -6221,8 +7549,14 @@
       <c r="E168" s="3" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="169" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F168">
+        <v>13.612299999999999</v>
+      </c>
+      <c r="G168">
+        <v>100.7012</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="4">
         <v>168</v>
       </c>
@@ -6238,8 +7572,14 @@
       <c r="E169" s="5" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="170" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F169">
+        <v>13.597799999999999</v>
+      </c>
+      <c r="G169">
+        <v>100.59780000000001</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
         <v>169</v>
       </c>
@@ -6255,8 +7595,14 @@
       <c r="E170" s="3" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="171" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F170">
+        <v>13.6234</v>
+      </c>
+      <c r="G170">
+        <v>100.76779999999999</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="4">
         <v>170</v>
       </c>
@@ -6272,8 +7618,14 @@
       <c r="E171" s="5" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="172" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F171">
+        <v>13.6212</v>
+      </c>
+      <c r="G171">
+        <v>100.6789</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
         <v>171</v>
       </c>
@@ -6289,8 +7641,14 @@
       <c r="E172" s="3" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="173" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F172">
+        <v>13.6456</v>
+      </c>
+      <c r="G172">
+        <v>100.7234</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="4">
         <v>172</v>
       </c>
@@ -6306,8 +7664,14 @@
       <c r="E173" s="5" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="174" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F173">
+        <v>13.6012</v>
+      </c>
+      <c r="G173">
+        <v>100.65430000000001</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <v>173</v>
       </c>
@@ -6323,8 +7687,14 @@
       <c r="E174" s="3" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="175" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F174">
+        <v>13.5876</v>
+      </c>
+      <c r="G174">
+        <v>100.7543</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="4">
         <v>174</v>
       </c>
@@ -6340,8 +7710,14 @@
       <c r="E175" s="5" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="176" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F175">
+        <v>13.6256</v>
+      </c>
+      <c r="G175">
+        <v>100.6978</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
         <v>175</v>
       </c>
@@ -6357,8 +7733,14 @@
       <c r="E176" s="3" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="177" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F176">
+        <v>13.595599999999999</v>
+      </c>
+      <c r="G176">
+        <v>100.5956</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="4">
         <v>176</v>
       </c>
@@ -6374,8 +7756,14 @@
       <c r="E177" s="5" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="178" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F177">
+        <v>13.607799999999999</v>
+      </c>
+      <c r="G177">
+        <v>100.60120000000001</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>177</v>
       </c>
@@ -6391,8 +7779,14 @@
       <c r="E178" s="3" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="179" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F178">
+        <v>13.654299999999999</v>
+      </c>
+      <c r="G178">
+        <v>100.6345</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
         <v>178</v>
       </c>
@@ -6408,8 +7802,14 @@
       <c r="E179" s="5" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="180" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F179">
+        <v>13.6456</v>
+      </c>
+      <c r="G179">
+        <v>100.59780000000001</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
         <v>179</v>
       </c>
@@ -6425,8 +7825,14 @@
       <c r="E180" s="3" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="181" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F180">
+        <v>13.578900000000001</v>
+      </c>
+      <c r="G180">
+        <v>100.5789</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
         <v>180</v>
       </c>
@@ -6442,8 +7848,14 @@
       <c r="E181" s="5" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="182" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F181">
+        <v>13.634499999999999</v>
+      </c>
+      <c r="G181">
+        <v>100.53449999999999</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>181</v>
       </c>
@@ -6459,8 +7871,14 @@
       <c r="E182" s="3" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="183" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F182">
+        <v>13.597799999999999</v>
+      </c>
+      <c r="G182">
+        <v>100.60120000000001</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="4">
         <v>182</v>
       </c>
@@ -6476,8 +7894,14 @@
       <c r="E183" s="5" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="184" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F183">
+        <v>13.6212</v>
+      </c>
+      <c r="G183">
+        <v>100.5789</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
         <v>183</v>
       </c>
@@ -6493,8 +7917,14 @@
       <c r="E184" s="3" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="185" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F184">
+        <v>13.523400000000001</v>
+      </c>
+      <c r="G184">
+        <v>99.812299999999993</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="4">
         <v>184</v>
       </c>
@@ -6510,8 +7940,14 @@
       <c r="E185" s="5" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="186" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F185">
+        <v>13.634499999999999</v>
+      </c>
+      <c r="G185">
+        <v>100.2543</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <v>185</v>
       </c>
@@ -6527,8 +7963,14 @@
       <c r="E186" s="3" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="187" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F186">
+        <v>13.543200000000001</v>
+      </c>
+      <c r="G186">
+        <v>100.1234</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
         <v>186</v>
       </c>
@@ -6544,8 +7986,14 @@
       <c r="E187" s="5" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="188" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F187">
+        <v>13.543200000000001</v>
+      </c>
+      <c r="G187">
+        <v>100.27889999999999</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
         <v>187</v>
       </c>
@@ -6561,8 +8009,14 @@
       <c r="E188" s="3" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="189" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F188">
+        <v>13.712300000000001</v>
+      </c>
+      <c r="G188">
+        <v>100.32340000000001</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="4">
         <v>188</v>
       </c>
@@ -6578,8 +8032,14 @@
       <c r="E189" s="5" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="190" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F189">
+        <v>13.6876</v>
+      </c>
+      <c r="G189">
+        <v>100.2876</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
         <v>189</v>
       </c>
@@ -6595,8 +8055,14 @@
       <c r="E190" s="3" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="191" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F190">
+        <v>13.547800000000001</v>
+      </c>
+      <c r="G190">
+        <v>100.2876</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="4">
         <v>190</v>
       </c>
@@ -6612,8 +8078,14 @@
       <c r="E191" s="5" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="192" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F191">
+        <v>13.712300000000001</v>
+      </c>
+      <c r="G191">
+        <v>100.2876</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
         <v>191</v>
       </c>
@@ -6629,8 +8101,14 @@
       <c r="E192" s="3" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="193" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F192">
+        <v>13.5345</v>
+      </c>
+      <c r="G192">
+        <v>100.26779999999999</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="4">
         <v>192</v>
       </c>
@@ -6646,8 +8124,14 @@
       <c r="E193" s="5" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="194" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F193">
+        <v>13.8123</v>
+      </c>
+      <c r="G193">
+        <v>102.06780000000001</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
         <v>193</v>
       </c>
@@ -6663,8 +8147,14 @@
       <c r="E194" s="3" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="195" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F194">
+        <v>14.734500000000001</v>
+      </c>
+      <c r="G194">
+        <v>100.7876</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="4">
         <v>194</v>
       </c>
@@ -6680,8 +8170,14 @@
       <c r="E195" s="5" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="196" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F195">
+        <v>14.523400000000001</v>
+      </c>
+      <c r="G195">
+        <v>100.9123</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
         <v>195</v>
       </c>
@@ -6697,8 +8193,14 @@
       <c r="E196" s="3" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="197" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F196">
+        <v>14.5345</v>
+      </c>
+      <c r="G196">
+        <v>100.9234</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="4">
         <v>196</v>
       </c>
@@ -6714,8 +8216,14 @@
       <c r="E197" s="5" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="198" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F197">
+        <v>14.887600000000001</v>
+      </c>
+      <c r="G197">
+        <v>100.38760000000001</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
         <v>197</v>
       </c>
@@ -6731,8 +8239,14 @@
       <c r="E198" s="3" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="199" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F198">
+        <v>15.023400000000001</v>
+      </c>
+      <c r="G198">
+        <v>100.33450000000001</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="4">
         <v>198</v>
       </c>
@@ -6748,8 +8262,14 @@
       <c r="E199" s="5" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="200" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F199">
+        <v>17.154299999999999</v>
+      </c>
+      <c r="G199">
+        <v>99.823400000000007</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
         <v>199</v>
       </c>
@@ -6765,8 +8285,14 @@
       <c r="E200" s="3" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="201" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F200">
+        <v>17.001200000000001</v>
+      </c>
+      <c r="G200">
+        <v>99.823400000000007</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="4">
         <v>200</v>
       </c>
@@ -6782,8 +8308,14 @@
       <c r="E201" s="5" t="s">
         <v>616</v>
       </c>
-    </row>
-    <row r="202" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F201">
+        <v>14.478899999999999</v>
+      </c>
+      <c r="G201">
+        <v>100.1123</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
         <v>201</v>
       </c>
@@ -6799,8 +8331,14 @@
       <c r="E202" s="3" t="s">
         <v>616</v>
       </c>
-    </row>
-    <row r="203" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F202">
+        <v>14.345599999999999</v>
+      </c>
+      <c r="G202">
+        <v>99.912300000000002</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="4">
         <v>202</v>
       </c>
@@ -6816,8 +8354,14 @@
       <c r="E203" s="5" t="s">
         <v>616</v>
       </c>
-    </row>
-    <row r="204" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F203">
+        <v>14.3789</v>
+      </c>
+      <c r="G203">
+        <v>99.887600000000006</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
         <v>203</v>
       </c>
@@ -6833,8 +8377,14 @@
       <c r="E204" s="3" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="205" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F204">
+        <v>9.5344999999999995</v>
+      </c>
+      <c r="G204">
+        <v>99.967799999999997</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="4">
         <v>204</v>
       </c>
@@ -6850,8 +8400,14 @@
       <c r="E205" s="5" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="206" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F205">
+        <v>9.1344999999999992</v>
+      </c>
+      <c r="G205">
+        <v>99.323400000000007</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
         <v>205</v>
       </c>
@@ -6867,8 +8423,14 @@
       <c r="E206" s="3" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="207" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F206">
+        <v>9.1789000000000005</v>
+      </c>
+      <c r="G206">
+        <v>99.454300000000003</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="4">
         <v>206</v>
       </c>
@@ -6884,8 +8446,14 @@
       <c r="E207" s="5" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="208" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F207">
+        <v>9.5542999999999996</v>
+      </c>
+      <c r="G207">
+        <v>100.0234</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
         <v>207</v>
       </c>
@@ -6901,8 +8469,14 @@
       <c r="E208" s="3" t="s">
         <v>634</v>
       </c>
-    </row>
-    <row r="209" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F208">
+        <v>14.8789</v>
+      </c>
+      <c r="G208">
+        <v>103.4876</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="4">
         <v>208</v>
       </c>
@@ -6918,8 +8492,14 @@
       <c r="E209" s="5" t="s">
         <v>637</v>
       </c>
-    </row>
-    <row r="210" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F209">
+        <v>17.845600000000001</v>
+      </c>
+      <c r="G209">
+        <v>102.5789</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
         <v>209</v>
       </c>
@@ -6935,8 +8515,14 @@
       <c r="E210" s="3" t="s">
         <v>637</v>
       </c>
-    </row>
-    <row r="211" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F210">
+        <v>17.8765</v>
+      </c>
+      <c r="G210">
+        <v>102.7345</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="4">
         <v>210</v>
       </c>
@@ -6952,8 +8538,14 @@
       <c r="E211" s="5" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="212" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F211">
+        <v>17.2012</v>
+      </c>
+      <c r="G211">
+        <v>102.4345</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
         <v>211</v>
       </c>
@@ -6969,8 +8561,14 @@
       <c r="E212" s="3" t="s">
         <v>622</v>
       </c>
-    </row>
-    <row r="213" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F212">
+        <v>14.5876</v>
+      </c>
+      <c r="G212">
+        <v>100.4543</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="4">
         <v>212</v>
       </c>
@@ -6986,8 +8584,14 @@
       <c r="E213" s="5" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="214" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F213">
+        <v>15.867800000000001</v>
+      </c>
+      <c r="G213">
+        <v>104.6234</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
         <v>213</v>
       </c>
@@ -7003,8 +8607,14 @@
       <c r="E214" s="3" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="215" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F214">
+        <v>17.112300000000001</v>
+      </c>
+      <c r="G214">
+        <v>102.85429999999999</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="4">
         <v>214</v>
       </c>
@@ -7020,8 +8630,14 @@
       <c r="E215" s="5" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="216" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F215">
+        <v>17.387599999999999</v>
+      </c>
+      <c r="G215">
+        <v>102.7876</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
         <v>215</v>
       </c>
@@ -7037,8 +8653,14 @@
       <c r="E216" s="3" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="217" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F216">
+        <v>17.412299999999998</v>
+      </c>
+      <c r="G216">
+        <v>102.7876</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="4">
         <v>216</v>
       </c>
@@ -7054,8 +8676,14 @@
       <c r="E217" s="5" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="218" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F217">
+        <v>17.9543</v>
+      </c>
+      <c r="G217">
+        <v>103.2456</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
         <v>217</v>
       </c>
@@ -7071,8 +8699,14 @@
       <c r="E218" s="3" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="219" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F218">
+        <v>17.6234</v>
+      </c>
+      <c r="G218">
+        <v>100.10120000000001</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="4">
         <v>218</v>
       </c>
@@ -7088,8 +8722,14 @@
       <c r="E219" s="5" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="220" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F219">
+        <v>15.3789</v>
+      </c>
+      <c r="G219">
+        <v>100.0234</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
         <v>219</v>
       </c>
@@ -7105,8 +8745,14 @@
       <c r="E220" s="3" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="221" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F220">
+        <v>15.2234</v>
+      </c>
+      <c r="G220">
+        <v>104.85429999999999</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
         <v>220</v>
       </c>
@@ -7122,8 +8768,14 @@
       <c r="E221" s="5" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="222" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F221">
+        <v>15.178900000000001</v>
+      </c>
+      <c r="G221">
+        <v>104.87649999999999</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
         <v>221</v>
       </c>
@@ -7139,8 +8791,14 @@
       <c r="E222" s="3" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="223" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F222">
+        <v>15.2234</v>
+      </c>
+      <c r="G222">
+        <v>104.85429999999999</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="4">
         <v>222</v>
       </c>
@@ -7155,6 +8813,12 @@
       </c>
       <c r="E223" s="5" t="s">
         <v>672</v>
+      </c>
+      <c r="F223">
+        <v>14.9345</v>
+      </c>
+      <c r="G223">
+        <v>105.0789</v>
       </c>
     </row>
   </sheetData>
